--- a/research/traditional_assets/database/data/belgium/belgium_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_electrical_equipment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1022812604878216</v>
+        <v>0.102059307336602</v>
       </c>
       <c r="C2">
-        <v>2657.94663374149</v>
+        <v>2637.237124462757</v>
       </c>
       <c r="D2">
-        <v>2657.94663374149</v>
+        <v>2665.031124462757</v>
       </c>
       <c r="E2">
-        <v>-724.7</v>
+        <v>-696.9060000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27.794</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1451,28 +1451,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3980382</v>
       </c>
       <c r="N2">
-        <v>357.7799999999999</v>
+        <v>356.3819617999999</v>
       </c>
       <c r="O2">
-        <v>89.44499999999998</v>
+        <v>89.09549044999999</v>
       </c>
       <c r="P2">
-        <v>268.3349999999999</v>
+        <v>267.2864713499999</v>
       </c>
       <c r="Q2">
-        <v>272.0549999999999</v>
+        <v>271.00647135</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1022812604878216</v>
+        <v>0.1027091488248505</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.109265235539342</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>255.9157539472097</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.102059307336602</v>
+        <v>0.1018373541853825</v>
       </c>
       <c r="C3">
-        <v>2637.237124462757</v>
+        <v>2616.56548211642</v>
       </c>
       <c r="D3">
-        <v>2665.031124462757</v>
+        <v>2672.15348211642</v>
       </c>
       <c r="E3">
-        <v>-696.9060000000001</v>
+        <v>-669.1120000000001</v>
       </c>
       <c r="F3">
-        <v>27.794</v>
+        <v>55.58799999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1533,28 +1533,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M3">
-        <v>1.3980382</v>
+        <v>2.7960764</v>
       </c>
       <c r="N3">
-        <v>356.3819617999999</v>
+        <v>354.9839235999999</v>
       </c>
       <c r="O3">
-        <v>89.09549044999999</v>
+        <v>88.74598089999998</v>
       </c>
       <c r="P3">
-        <v>267.2864713499999</v>
+        <v>266.2379427</v>
       </c>
       <c r="Q3">
-        <v>271.00647135</v>
+        <v>269.9579427</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1027091488248505</v>
+        <v>0.1031457695769209</v>
       </c>
       <c r="T3">
-        <v>1.109265235539342</v>
+        <v>1.117775786678971</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>255.9157539472097</v>
+        <v>127.9578769736049</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1018373541853825</v>
+        <v>0.1016154010341629</v>
       </c>
       <c r="C4">
-        <v>2616.56548211642</v>
+        <v>2595.932011116805</v>
       </c>
       <c r="D4">
-        <v>2672.15348211642</v>
+        <v>2679.314011116805</v>
       </c>
       <c r="E4">
-        <v>-669.1120000000001</v>
+        <v>-641.3180000000001</v>
       </c>
       <c r="F4">
-        <v>55.58799999999999</v>
+        <v>83.38199999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1615,28 +1615,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M4">
-        <v>2.7960764</v>
+        <v>4.194114599999999</v>
       </c>
       <c r="N4">
-        <v>354.9839235999999</v>
+        <v>353.5858853999999</v>
       </c>
       <c r="O4">
-        <v>88.74598089999998</v>
+        <v>88.39647134999998</v>
       </c>
       <c r="P4">
-        <v>266.2379427</v>
+        <v>265.18941405</v>
       </c>
       <c r="Q4">
-        <v>269.9579427</v>
+        <v>268.90941405</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1031457695769209</v>
+        <v>0.1035913928187246</v>
       </c>
       <c r="T4">
-        <v>1.117775786678971</v>
+        <v>1.126461813099831</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>127.9578769736049</v>
+        <v>85.30525131573658</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1016154010341629</v>
+        <v>0.1013934478829433</v>
       </c>
       <c r="C5">
-        <v>2595.932011116805</v>
+        <v>2575.337019149944</v>
       </c>
       <c r="D5">
-        <v>2679.314011116805</v>
+        <v>2686.513019149944</v>
       </c>
       <c r="E5">
-        <v>-641.3180000000001</v>
+        <v>-613.5240000000001</v>
       </c>
       <c r="F5">
-        <v>83.38199999999999</v>
+        <v>111.176</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1697,28 +1697,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M5">
-        <v>4.194114599999999</v>
+        <v>5.592152799999999</v>
       </c>
       <c r="N5">
-        <v>353.5858853999999</v>
+        <v>352.1878471999999</v>
       </c>
       <c r="O5">
-        <v>88.39647134999998</v>
+        <v>88.04696179999998</v>
       </c>
       <c r="P5">
-        <v>265.18941405</v>
+        <v>264.1408853999999</v>
       </c>
       <c r="Q5">
-        <v>268.90941405</v>
+        <v>267.8608854</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1035913928187246</v>
+        <v>0.104046299878066</v>
       </c>
       <c r="T5">
-        <v>1.126461813099831</v>
+        <v>1.135328798404458</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>85.30525131573658</v>
+        <v>63.97893848680243</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1013934478829433</v>
+        <v>0.1011714947317238</v>
       </c>
       <c r="C6">
-        <v>2575.337019149944</v>
+        <v>2554.780817217645</v>
       </c>
       <c r="D6">
-        <v>2686.513019149944</v>
+        <v>2693.750817217644</v>
       </c>
       <c r="E6">
-        <v>-613.5240000000001</v>
+        <v>-585.73</v>
       </c>
       <c r="F6">
-        <v>111.176</v>
+        <v>138.97</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1779,28 +1779,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M6">
-        <v>5.592152799999999</v>
+        <v>6.990190999999999</v>
       </c>
       <c r="N6">
-        <v>352.1878471999999</v>
+        <v>350.7898089999999</v>
       </c>
       <c r="O6">
-        <v>88.04696179999998</v>
+        <v>87.69745224999998</v>
       </c>
       <c r="P6">
-        <v>264.1408853999999</v>
+        <v>263.09235675</v>
       </c>
       <c r="Q6">
-        <v>267.8608854</v>
+        <v>266.81235675</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.104046299878066</v>
+        <v>0.1045107839281303</v>
       </c>
       <c r="T6">
-        <v>1.135328798404458</v>
+        <v>1.144382457083919</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.97893848680243</v>
+        <v>51.18315078944195</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1011714947317238</v>
+        <v>0.1009495415805042</v>
       </c>
       <c r="C7">
-        <v>2554.780817217645</v>
+        <v>2534.263719682277</v>
       </c>
       <c r="D7">
-        <v>2693.750817217644</v>
+        <v>2701.027719682278</v>
       </c>
       <c r="E7">
-        <v>-585.73</v>
+        <v>-557.936</v>
       </c>
       <c r="F7">
-        <v>138.97</v>
+        <v>166.764</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1861,28 +1861,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M7">
-        <v>6.990190999999999</v>
+        <v>8.388229199999998</v>
       </c>
       <c r="N7">
-        <v>350.7898089999999</v>
+        <v>349.3917707999999</v>
       </c>
       <c r="O7">
-        <v>87.69745224999998</v>
+        <v>87.34794269999998</v>
       </c>
       <c r="P7">
-        <v>263.09235675</v>
+        <v>262.0438280999999</v>
       </c>
       <c r="Q7">
-        <v>266.81235675</v>
+        <v>265.7638281</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1045107839281303</v>
+        <v>0.1049851506175577</v>
       </c>
       <c r="T7">
-        <v>1.144382457083919</v>
+        <v>1.153628746799114</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.18315078944195</v>
+        <v>42.65262565786829</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1009495415805042</v>
+        <v>0.1007275884292847</v>
       </c>
       <c r="C8">
-        <v>2534.263719682277</v>
+        <v>2513.786044312292</v>
       </c>
       <c r="D8">
-        <v>2701.027719682278</v>
+        <v>2708.344044312292</v>
       </c>
       <c r="E8">
-        <v>-557.936</v>
+        <v>-530.1420000000001</v>
       </c>
       <c r="F8">
-        <v>166.764</v>
+        <v>194.558</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1943,28 +1943,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M8">
-        <v>8.388229199999998</v>
+        <v>9.786267399999998</v>
       </c>
       <c r="N8">
-        <v>349.3917707999999</v>
+        <v>347.9937325999999</v>
       </c>
       <c r="O8">
-        <v>87.34794269999998</v>
+        <v>86.99843314999998</v>
       </c>
       <c r="P8">
-        <v>262.0438280999999</v>
+        <v>260.9952994499999</v>
       </c>
       <c r="Q8">
-        <v>265.7638281</v>
+        <v>264.71529945</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1049851506175577</v>
+        <v>0.1054697187411663</v>
       </c>
       <c r="T8">
-        <v>1.153628746799114</v>
+        <v>1.16307388145442</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.65262565786829</v>
+        <v>36.55939342102996</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1007275884292847</v>
+        <v>0.1005056352780651</v>
       </c>
       <c r="C9">
-        <v>2513.786044312292</v>
+        <v>2493.348112328469</v>
       </c>
       <c r="D9">
-        <v>2708.344044312292</v>
+        <v>2715.700112328469</v>
       </c>
       <c r="E9">
-        <v>-530.1420000000001</v>
+        <v>-502.3480000000001</v>
       </c>
       <c r="F9">
-        <v>194.558</v>
+        <v>222.352</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2025,28 +2025,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M9">
-        <v>9.7862674</v>
+        <v>11.1843056</v>
       </c>
       <c r="N9">
-        <v>347.9937325999999</v>
+        <v>346.5956943999999</v>
       </c>
       <c r="O9">
-        <v>86.99843314999998</v>
+        <v>86.64892359999997</v>
       </c>
       <c r="P9">
-        <v>260.9952994499999</v>
+        <v>259.9467707999999</v>
       </c>
       <c r="Q9">
-        <v>264.71529945</v>
+        <v>263.6667707999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1054697187411663</v>
+        <v>0.1059648209544186</v>
       </c>
       <c r="T9">
-        <v>1.16307388145442</v>
+        <v>1.172724345123972</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.55939342102996</v>
+        <v>31.98946924340121</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1005056352780651</v>
+        <v>0.1002836821268456</v>
       </c>
       <c r="C10">
-        <v>2493.348112328469</v>
+        <v>2472.950248450934</v>
       </c>
       <c r="D10">
-        <v>2715.700112328469</v>
+        <v>2723.096248450934</v>
       </c>
       <c r="E10">
-        <v>-502.3480000000001</v>
+        <v>-474.5540000000001</v>
       </c>
       <c r="F10">
-        <v>222.352</v>
+        <v>250.146</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2107,28 +2107,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M10">
-        <v>11.1843056</v>
+        <v>12.5823438</v>
       </c>
       <c r="N10">
-        <v>346.5956943999999</v>
+        <v>345.1976561999999</v>
       </c>
       <c r="O10">
-        <v>86.64892359999997</v>
+        <v>86.29941404999998</v>
       </c>
       <c r="P10">
-        <v>259.9467707999999</v>
+        <v>258.8982421499999</v>
       </c>
       <c r="Q10">
-        <v>263.6667707999999</v>
+        <v>262.61824215</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1059648209544186</v>
+        <v>0.1064708045349951</v>
       </c>
       <c r="T10">
-        <v>1.172724345123972</v>
+        <v>1.182586906896152</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.98946924340121</v>
+        <v>28.43508377191219</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1002836821268456</v>
+        <v>0.100061728975626</v>
       </c>
       <c r="C11">
-        <v>2472.950248450934</v>
+        <v>2452.592780946939</v>
       </c>
       <c r="D11">
-        <v>2723.096248450934</v>
+        <v>2730.532780946939</v>
       </c>
       <c r="E11">
-        <v>-474.5540000000001</v>
+        <v>-446.7600000000001</v>
       </c>
       <c r="F11">
-        <v>250.146</v>
+        <v>277.9399999999999</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2189,28 +2189,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M11">
-        <v>12.5823438</v>
+        <v>13.980382</v>
       </c>
       <c r="N11">
-        <v>345.1976561999999</v>
+        <v>343.7996179999999</v>
       </c>
       <c r="O11">
-        <v>86.29941404999998</v>
+        <v>85.94990449999997</v>
       </c>
       <c r="P11">
-        <v>258.8982421499999</v>
+        <v>257.8497134999999</v>
       </c>
       <c r="Q11">
-        <v>262.61824215</v>
+        <v>261.5697134999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1064708045349951</v>
+        <v>0.10698803219514</v>
       </c>
       <c r="T11">
-        <v>1.182586906896152</v>
+        <v>1.192668636707713</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.43508377191219</v>
+        <v>25.59157539472097</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.100061728975626</v>
+        <v>0.09983977582440647</v>
       </c>
       <c r="C12">
-        <v>2452.592780946939</v>
+        <v>2432.276041679431</v>
       </c>
       <c r="D12">
-        <v>2730.532780946939</v>
+        <v>2738.010041679431</v>
       </c>
       <c r="E12">
-        <v>-446.76</v>
+        <v>-418.9660000000001</v>
       </c>
       <c r="F12">
-        <v>277.94</v>
+        <v>305.734</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2271,28 +2271,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M12">
-        <v>13.980382</v>
+        <v>15.3784202</v>
       </c>
       <c r="N12">
-        <v>343.7996179999999</v>
+        <v>342.4015797999999</v>
       </c>
       <c r="O12">
-        <v>85.94990449999997</v>
+        <v>85.60039494999998</v>
       </c>
       <c r="P12">
-        <v>257.8497134999999</v>
+        <v>256.8011848499999</v>
       </c>
       <c r="Q12">
-        <v>261.5697134999999</v>
+        <v>260.5211848499999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.10698803219514</v>
+        <v>0.1075168829487713</v>
       </c>
       <c r="T12">
-        <v>1.192668636707713</v>
+        <v>1.202976922245377</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.59157539472097</v>
+        <v>23.26506854065543</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09983977582440647</v>
+        <v>0.09961782267318692</v>
       </c>
       <c r="C13">
-        <v>2432.276041679431</v>
+        <v>2412.000366156416</v>
       </c>
       <c r="D13">
-        <v>2738.010041679431</v>
+        <v>2745.528366156416</v>
       </c>
       <c r="E13">
-        <v>-418.9660000000001</v>
+        <v>-391.1720000000001</v>
       </c>
       <c r="F13">
-        <v>305.734</v>
+        <v>333.528</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2353,28 +2353,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M13">
-        <v>15.3784202</v>
+        <v>16.7764584</v>
       </c>
       <c r="N13">
-        <v>342.4015797999999</v>
+        <v>341.0035415999999</v>
       </c>
       <c r="O13">
-        <v>85.60039494999998</v>
+        <v>85.25088539999999</v>
       </c>
       <c r="P13">
-        <v>256.8011848499999</v>
+        <v>255.7526562</v>
       </c>
       <c r="Q13">
-        <v>260.5211848499999</v>
+        <v>259.4726562</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1075168829487713</v>
+        <v>0.1080577530377124</v>
       </c>
       <c r="T13">
-        <v>1.202976922245377</v>
+        <v>1.213519486999806</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.26506854065543</v>
+        <v>21.32631282893415</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09961782267318692</v>
+        <v>0.09939586952196736</v>
       </c>
       <c r="C14">
-        <v>2412.000366156416</v>
+        <v>2391.766093581145</v>
       </c>
       <c r="D14">
-        <v>2745.528366156416</v>
+        <v>2753.088093581145</v>
       </c>
       <c r="E14">
-        <v>-391.1720000000001</v>
+        <v>-363.3780000000001</v>
       </c>
       <c r="F14">
-        <v>333.528</v>
+        <v>361.3219999999999</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2435,28 +2435,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M14">
-        <v>16.7764584</v>
+        <v>18.1744966</v>
       </c>
       <c r="N14">
-        <v>341.0035415999999</v>
+        <v>339.6055033999999</v>
       </c>
       <c r="O14">
-        <v>85.25088539999999</v>
+        <v>84.90137584999998</v>
       </c>
       <c r="P14">
-        <v>255.7526562</v>
+        <v>254.70412755</v>
       </c>
       <c r="Q14">
-        <v>259.4726562</v>
+        <v>258.42412755</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1080577530377124</v>
+        <v>0.1086110569218016</v>
       </c>
       <c r="T14">
-        <v>1.213519486999806</v>
+        <v>1.224304409564682</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.32631282893415</v>
+        <v>19.68582722670844</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09939586952196736</v>
+        <v>0.09917391637074778</v>
       </c>
       <c r="C15">
-        <v>2391.766093581145</v>
+        <v>2371.573566903127</v>
       </c>
       <c r="D15">
-        <v>2753.088093581145</v>
+        <v>2760.689566903127</v>
       </c>
       <c r="E15">
-        <v>-363.3780000000001</v>
+        <v>-335.5840000000001</v>
       </c>
       <c r="F15">
-        <v>361.3219999999999</v>
+        <v>389.116</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2517,28 +2517,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M15">
-        <v>18.1744966</v>
+        <v>19.5725348</v>
       </c>
       <c r="N15">
-        <v>339.6055033999999</v>
+        <v>338.2074651999999</v>
       </c>
       <c r="O15">
-        <v>84.90137584999998</v>
+        <v>84.55186629999997</v>
       </c>
       <c r="P15">
-        <v>254.70412755</v>
+        <v>253.6555988999999</v>
       </c>
       <c r="Q15">
-        <v>258.42412755</v>
+        <v>257.3755988999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1086110569218016</v>
+        <v>0.1091772283380788</v>
       </c>
       <c r="T15">
-        <v>1.224304409564682</v>
+        <v>1.235340144282229</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.68582722670844</v>
+        <v>18.27969671051498</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09917391637074778</v>
+        <v>0.09895196321952826</v>
       </c>
       <c r="C16">
-        <v>2371.573566903127</v>
+        <v>2351.423132869988</v>
       </c>
       <c r="D16">
-        <v>2760.689566903127</v>
+        <v>2768.333132869988</v>
       </c>
       <c r="E16">
-        <v>-335.5840000000001</v>
+        <v>-307.79</v>
       </c>
       <c r="F16">
-        <v>389.116</v>
+        <v>416.91</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2599,28 +2599,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M16">
-        <v>19.5725348</v>
+        <v>20.970573</v>
       </c>
       <c r="N16">
-        <v>338.2074651999999</v>
+        <v>336.8094269999999</v>
       </c>
       <c r="O16">
-        <v>84.55186629999997</v>
+        <v>84.20235674999998</v>
       </c>
       <c r="P16">
-        <v>253.6555988999999</v>
+        <v>252.6070702499999</v>
       </c>
       <c r="Q16">
-        <v>257.3755988999999</v>
+        <v>256.32707025</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1091772283380788</v>
+        <v>0.1097567214347391</v>
       </c>
       <c r="T16">
-        <v>1.235340144282229</v>
+        <v>1.246635543346071</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.27969671051498</v>
+        <v>17.06105026314731</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09895196321952826</v>
+        <v>0.09873001006830869</v>
       </c>
       <c r="C17">
-        <v>2351.423132869988</v>
+        <v>2331.315142080203</v>
       </c>
       <c r="D17">
-        <v>2768.333132869988</v>
+        <v>2776.019142080203</v>
       </c>
       <c r="E17">
-        <v>-307.7900000000001</v>
+        <v>-279.9960000000001</v>
       </c>
       <c r="F17">
-        <v>416.9099999999999</v>
+        <v>444.704</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2681,28 +2681,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M17">
-        <v>20.97057299999999</v>
+        <v>22.3686112</v>
       </c>
       <c r="N17">
-        <v>336.8094269999999</v>
+        <v>335.4113887999999</v>
       </c>
       <c r="O17">
-        <v>84.20235674999998</v>
+        <v>83.85284719999999</v>
       </c>
       <c r="P17">
-        <v>252.6070702499999</v>
+        <v>251.5585416</v>
       </c>
       <c r="Q17">
-        <v>256.32707025</v>
+        <v>255.2785416</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1097567214347391</v>
+        <v>0.1103500119860818</v>
       </c>
       <c r="T17">
-        <v>1.246635543346071</v>
+        <v>1.258199880482862</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.06105026314732</v>
+        <v>15.99473462170061</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09873001006830869</v>
+        <v>0.09850805691708915</v>
       </c>
       <c r="C18">
-        <v>2331.315142080203</v>
+        <v>2311.249949036694</v>
       </c>
       <c r="D18">
-        <v>2776.019142080203</v>
+        <v>2783.747949036694</v>
       </c>
       <c r="E18">
-        <v>-279.9960000000001</v>
+        <v>-252.2020000000001</v>
       </c>
       <c r="F18">
-        <v>444.704</v>
+        <v>472.498</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2763,28 +2763,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M18">
-        <v>22.3686112</v>
+        <v>23.7666494</v>
       </c>
       <c r="N18">
-        <v>335.4113887999999</v>
+        <v>334.0133505999999</v>
       </c>
       <c r="O18">
-        <v>83.85284719999999</v>
+        <v>83.50333764999998</v>
       </c>
       <c r="P18">
-        <v>251.5585416</v>
+        <v>250.5100129499999</v>
       </c>
       <c r="Q18">
-        <v>255.2785416</v>
+        <v>254.2300129499999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1103500119860818</v>
+        <v>0.1109575986952882</v>
       </c>
       <c r="T18">
-        <v>1.258199880482862</v>
+        <v>1.270042876345841</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.99473462170061</v>
+        <v>15.05386787924763</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09850805691708915</v>
+        <v>0.09828610376586958</v>
       </c>
       <c r="C19">
-        <v>2311.249949036694</v>
+        <v>2291.227912201343</v>
       </c>
       <c r="D19">
-        <v>2783.747949036694</v>
+        <v>2791.519912201343</v>
       </c>
       <c r="E19">
-        <v>-252.2020000000001</v>
+        <v>-224.4080000000001</v>
       </c>
       <c r="F19">
-        <v>472.498</v>
+        <v>500.292</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2845,28 +2845,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M19">
-        <v>23.7666494</v>
+        <v>25.1646876</v>
       </c>
       <c r="N19">
-        <v>334.0133505999999</v>
+        <v>332.6153123999999</v>
       </c>
       <c r="O19">
-        <v>83.50333764999998</v>
+        <v>83.15382809999998</v>
       </c>
       <c r="P19">
-        <v>250.5100129499999</v>
+        <v>249.4614842999999</v>
       </c>
       <c r="Q19">
-        <v>254.2300129499999</v>
+        <v>253.1814842999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1109575986952882</v>
+        <v>0.1115800045925239</v>
       </c>
       <c r="T19">
-        <v>1.270042876345841</v>
+        <v>1.282174725766453</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.05386787924763</v>
+        <v>14.21754188595609</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09828610376586959</v>
+        <v>0.09806415061465006</v>
       </c>
       <c r="C20">
-        <v>2291.227912201342</v>
+        <v>2271.249394050402</v>
       </c>
       <c r="D20">
-        <v>2791.519912201342</v>
+        <v>2799.335394050402</v>
       </c>
       <c r="E20">
-        <v>-224.4080000000001</v>
+        <v>-196.6140000000001</v>
       </c>
       <c r="F20">
-        <v>500.2919999999999</v>
+        <v>528.0859999999999</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2927,28 +2927,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M20">
-        <v>25.16468759999999</v>
+        <v>26.56272579999999</v>
       </c>
       <c r="N20">
-        <v>332.6153123999999</v>
+        <v>331.2172741999999</v>
       </c>
       <c r="O20">
-        <v>83.15382809999998</v>
+        <v>82.80431854999998</v>
       </c>
       <c r="P20">
-        <v>249.4614842999999</v>
+        <v>248.4129556499999</v>
       </c>
       <c r="Q20">
-        <v>253.1814842999999</v>
+        <v>252.1329556499999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1115800045925239</v>
+        <v>0.112217778536605</v>
       </c>
       <c r="T20">
-        <v>1.282174725766453</v>
+        <v>1.294606127024612</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.2175418859561</v>
+        <v>13.46925020774788</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09806415061465006</v>
+        <v>0.09806719746343048</v>
       </c>
       <c r="C21">
-        <v>2271.249394050402</v>
+        <v>2243.347811246796</v>
       </c>
       <c r="D21">
-        <v>2799.335394050402</v>
+        <v>2799.227811246797</v>
       </c>
       <c r="E21">
-        <v>-196.6140000000001</v>
+        <v>-168.8200000000001</v>
       </c>
       <c r="F21">
-        <v>528.0859999999999</v>
+        <v>555.88</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3009,45 +3009,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M21">
-        <v>26.56272579999999</v>
+        <v>28.794584</v>
       </c>
       <c r="N21">
-        <v>331.2172741999999</v>
+        <v>328.9854159999999</v>
       </c>
       <c r="O21">
-        <v>82.80431854999998</v>
+        <v>82.24635399999998</v>
       </c>
       <c r="P21">
-        <v>248.4129556499999</v>
+        <v>246.7390619999999</v>
       </c>
       <c r="Q21">
-        <v>252.1329556499999</v>
+        <v>250.4590619999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.112217778536605</v>
+        <v>0.1128714968292881</v>
       </c>
       <c r="T21">
-        <v>1.294606127024612</v>
+        <v>1.307348313314224</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.46925020774788</v>
+        <v>12.42525330457978</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09806719746343048</v>
+        <v>0.09785649431221093</v>
       </c>
       <c r="C22">
-        <v>2243.347811246796</v>
+        <v>2223.013179779907</v>
       </c>
       <c r="D22">
-        <v>2799.227811246797</v>
+        <v>2806.687179779907</v>
       </c>
       <c r="E22">
-        <v>-168.8200000000001</v>
+        <v>-141.0260000000001</v>
       </c>
       <c r="F22">
-        <v>555.88</v>
+        <v>583.674</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3091,28 +3091,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M22">
-        <v>28.794584</v>
+        <v>30.2343132</v>
       </c>
       <c r="N22">
-        <v>328.9854159999999</v>
+        <v>327.5456867999999</v>
       </c>
       <c r="O22">
-        <v>82.24635399999998</v>
+        <v>81.88642169999999</v>
       </c>
       <c r="P22">
-        <v>246.7390619999999</v>
+        <v>245.6592651</v>
       </c>
       <c r="Q22">
-        <v>250.4590619999999</v>
+        <v>249.3792651</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1128714968292881</v>
+        <v>0.1135417649521657</v>
       </c>
       <c r="T22">
-        <v>1.307348313314224</v>
+        <v>1.32041308659851</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.42525330457978</v>
+        <v>11.83357457579026</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09785649431221093</v>
+        <v>0.09764579116099138</v>
       </c>
       <c r="C23">
-        <v>2223.013179779907</v>
+        <v>2202.718409913329</v>
       </c>
       <c r="D23">
-        <v>2806.687179779907</v>
+        <v>2814.186409913329</v>
       </c>
       <c r="E23">
-        <v>-141.0260000000002</v>
+        <v>-113.2320000000001</v>
       </c>
       <c r="F23">
-        <v>583.6739999999999</v>
+        <v>611.468</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3173,28 +3173,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M23">
-        <v>30.23431319999999</v>
+        <v>31.6740424</v>
       </c>
       <c r="N23">
-        <v>327.5456867999999</v>
+        <v>326.1059575999999</v>
       </c>
       <c r="O23">
-        <v>81.88642169999999</v>
+        <v>81.52648939999997</v>
       </c>
       <c r="P23">
-        <v>245.6592651</v>
+        <v>244.5794681999999</v>
       </c>
       <c r="Q23">
-        <v>249.3792651</v>
+        <v>248.2994681999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1135417649521657</v>
+        <v>0.1142292194371684</v>
       </c>
       <c r="T23">
-        <v>1.32041308659851</v>
+        <v>1.333812854069573</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.83357457579027</v>
+        <v>11.29568482234525</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09764579116099138</v>
+        <v>0.09743508800977183</v>
       </c>
       <c r="C24">
-        <v>2202.718409913329</v>
+        <v>2182.463822023528</v>
       </c>
       <c r="D24">
-        <v>2814.186409913329</v>
+        <v>2821.725822023528</v>
       </c>
       <c r="E24">
-        <v>-113.2320000000001</v>
+        <v>-85.4380000000001</v>
       </c>
       <c r="F24">
-        <v>611.468</v>
+        <v>639.2619999999999</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3255,28 +3255,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M24">
-        <v>31.6740424</v>
+        <v>33.1137716</v>
       </c>
       <c r="N24">
-        <v>326.1059575999999</v>
+        <v>324.6662283999999</v>
       </c>
       <c r="O24">
-        <v>81.52648939999997</v>
+        <v>81.16655709999998</v>
       </c>
       <c r="P24">
-        <v>244.5794681999999</v>
+        <v>243.4996712999999</v>
       </c>
       <c r="Q24">
-        <v>248.2994681999999</v>
+        <v>247.2196712999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1142292194371684</v>
+        <v>0.1149345298828205</v>
       </c>
       <c r="T24">
-        <v>1.333812854069573</v>
+        <v>1.347560667448974</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.29568482234525</v>
+        <v>10.80456809093893</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09743508800977183</v>
+        <v>0.09722438485855227</v>
       </c>
       <c r="C25">
-        <v>2182.463822023528</v>
+        <v>2162.249739929441</v>
       </c>
       <c r="D25">
-        <v>2821.725822023528</v>
+        <v>2829.305739929441</v>
       </c>
       <c r="E25">
-        <v>-85.4380000000001</v>
+        <v>-57.64400000000012</v>
       </c>
       <c r="F25">
-        <v>639.2619999999999</v>
+        <v>667.0559999999999</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3337,28 +3337,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M25">
-        <v>33.1137716</v>
+        <v>34.55350079999999</v>
       </c>
       <c r="N25">
-        <v>324.6662283999999</v>
+        <v>323.2264991999999</v>
       </c>
       <c r="O25">
-        <v>81.16655709999998</v>
+        <v>80.80662479999998</v>
       </c>
       <c r="P25">
-        <v>243.4996712999999</v>
+        <v>242.4198743999999</v>
       </c>
       <c r="Q25">
-        <v>247.2196712999999</v>
+        <v>246.1398743999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1149345298828205</v>
+        <v>0.115658401129674</v>
       </c>
       <c r="T25">
-        <v>1.347560667448974</v>
+        <v>1.361670265390992</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.80456809093893</v>
+        <v>10.35437775381648</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09722438485855227</v>
+        <v>0.09701368170733272</v>
       </c>
       <c r="C26">
-        <v>2162.249739929441</v>
+        <v>2142.076490938838</v>
       </c>
       <c r="D26">
-        <v>2829.305739929441</v>
+        <v>2836.926490938838</v>
       </c>
       <c r="E26">
-        <v>-57.64400000000012</v>
+        <v>-29.85000000000014</v>
       </c>
       <c r="F26">
-        <v>667.0559999999999</v>
+        <v>694.8499999999999</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3419,28 +3419,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M26">
-        <v>34.55350079999999</v>
+        <v>35.99323</v>
       </c>
       <c r="N26">
-        <v>323.2264991999999</v>
+        <v>321.7867699999999</v>
       </c>
       <c r="O26">
-        <v>80.80662479999998</v>
+        <v>80.44669249999998</v>
       </c>
       <c r="P26">
-        <v>242.4198743999999</v>
+        <v>241.3400774999999</v>
       </c>
       <c r="Q26">
-        <v>246.1398743999999</v>
+        <v>245.0600774999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.115658401129674</v>
+        <v>0.116401575609777</v>
       </c>
       <c r="T26">
-        <v>1.361670265390992</v>
+        <v>1.37615611927813</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.35437775381648</v>
+        <v>9.940202643663822</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09701368170733272</v>
+        <v>0.09713447855611317</v>
       </c>
       <c r="C27">
-        <v>2142.076490938838</v>
+        <v>2109.908474308566</v>
       </c>
       <c r="D27">
-        <v>2836.926490938838</v>
+        <v>2832.552474308566</v>
       </c>
       <c r="E27">
-        <v>-29.85000000000014</v>
+        <v>-2.056000000000154</v>
       </c>
       <c r="F27">
-        <v>694.8499999999999</v>
+        <v>722.6439999999999</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3501,45 +3501,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M27">
-        <v>35.99323</v>
+        <v>38.66145399999999</v>
       </c>
       <c r="N27">
-        <v>321.7867699999999</v>
+        <v>319.1185459999999</v>
       </c>
       <c r="O27">
-        <v>80.44669249999998</v>
+        <v>79.77963649999998</v>
       </c>
       <c r="P27">
-        <v>241.3400774999999</v>
+        <v>239.3389094999999</v>
       </c>
       <c r="Q27">
-        <v>245.0600774999999</v>
+        <v>243.0589094999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.116401575609777</v>
+        <v>0.1171648358866394</v>
       </c>
       <c r="T27">
-        <v>1.37615611927813</v>
+        <v>1.391033482729786</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.940202643663822</v>
+        <v>9.254178593490042</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09713447855611317</v>
+        <v>0.09693652540489361</v>
       </c>
       <c r="C28">
-        <v>2109.908474308566</v>
+        <v>2089.289373602207</v>
       </c>
       <c r="D28">
-        <v>2832.552474308566</v>
+        <v>2839.727373602207</v>
       </c>
       <c r="E28">
-        <v>-2.056000000000154</v>
+        <v>25.73799999999994</v>
       </c>
       <c r="F28">
-        <v>722.6439999999999</v>
+        <v>750.438</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3583,28 +3583,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M28">
-        <v>38.66145399999999</v>
+        <v>40.148433</v>
       </c>
       <c r="N28">
-        <v>319.1185459999999</v>
+        <v>317.6315669999999</v>
       </c>
       <c r="O28">
-        <v>79.77963649999998</v>
+        <v>79.40789174999998</v>
       </c>
       <c r="P28">
-        <v>239.3389094999999</v>
+        <v>238.2236752499999</v>
       </c>
       <c r="Q28">
-        <v>243.0589094999999</v>
+        <v>241.9436752499999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1171648358866394</v>
+        <v>0.1179490074039639</v>
       </c>
       <c r="T28">
-        <v>1.391033482729786</v>
+        <v>1.406318445180117</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.254178593490042</v>
+        <v>8.911431238175595</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09693652540489361</v>
+        <v>0.09673857225367405</v>
       </c>
       <c r="C29">
-        <v>2089.289373602207</v>
+        <v>2068.706713462469</v>
       </c>
       <c r="D29">
-        <v>2839.727373602207</v>
+        <v>2846.938713462469</v>
       </c>
       <c r="E29">
-        <v>25.73799999999994</v>
+        <v>53.53199999999993</v>
       </c>
       <c r="F29">
-        <v>750.438</v>
+        <v>778.232</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3665,28 +3665,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M29">
-        <v>40.148433</v>
+        <v>41.635412</v>
       </c>
       <c r="N29">
-        <v>317.6315669999999</v>
+        <v>316.1445879999999</v>
       </c>
       <c r="O29">
-        <v>79.40789174999998</v>
+        <v>79.03614699999999</v>
       </c>
       <c r="P29">
-        <v>238.2236752499999</v>
+        <v>237.108441</v>
       </c>
       <c r="Q29">
-        <v>241.9436752499999</v>
+        <v>240.828441</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1179490074039639</v>
+        <v>0.1187549614634362</v>
       </c>
       <c r="T29">
-        <v>1.406318445180117</v>
+        <v>1.422027989920735</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.911431238175595</v>
+        <v>8.593165836812183</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09673857225367405</v>
+        <v>0.0965406191024545</v>
       </c>
       <c r="C30">
-        <v>2068.706713462469</v>
+        <v>2048.160772212903</v>
       </c>
       <c r="D30">
-        <v>2846.938713462469</v>
+        <v>2854.186772212903</v>
       </c>
       <c r="E30">
-        <v>53.53199999999993</v>
+        <v>81.32599999999991</v>
       </c>
       <c r="F30">
-        <v>778.232</v>
+        <v>806.026</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3747,28 +3747,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M30">
-        <v>41.635412</v>
+        <v>43.12239099999999</v>
       </c>
       <c r="N30">
-        <v>316.1445879999999</v>
+        <v>314.6576089999999</v>
       </c>
       <c r="O30">
-        <v>79.03614699999999</v>
+        <v>78.66440224999998</v>
       </c>
       <c r="P30">
-        <v>237.108441</v>
+        <v>235.99320675</v>
       </c>
       <c r="Q30">
-        <v>240.828441</v>
+        <v>239.71320675</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1187549614634362</v>
+        <v>0.1195836184541613</v>
       </c>
       <c r="T30">
-        <v>1.422027989920735</v>
+        <v>1.438180057048412</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.593165836812183</v>
+        <v>8.296849773473831</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0965406191024545</v>
+        <v>0.09634266595123495</v>
       </c>
       <c r="C31">
-        <v>2048.160772212903</v>
+        <v>2027.651831018653</v>
       </c>
       <c r="D31">
-        <v>2854.186772212903</v>
+        <v>2861.471831018653</v>
       </c>
       <c r="E31">
-        <v>81.32599999999979</v>
+        <v>109.1199999999998</v>
       </c>
       <c r="F31">
-        <v>806.0259999999998</v>
+        <v>833.8199999999998</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3829,28 +3829,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M31">
-        <v>43.12239099999999</v>
+        <v>44.60936999999999</v>
       </c>
       <c r="N31">
-        <v>314.6576089999999</v>
+        <v>313.1706299999999</v>
       </c>
       <c r="O31">
-        <v>78.66440224999998</v>
+        <v>78.29265749999998</v>
       </c>
       <c r="P31">
-        <v>235.99320675</v>
+        <v>234.8779724999999</v>
       </c>
       <c r="Q31">
-        <v>239.71320675</v>
+        <v>238.5979724999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1195836184541613</v>
+        <v>0.1204359513589071</v>
       </c>
       <c r="T31">
-        <v>1.438180057048412</v>
+        <v>1.454793611808309</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.296849773473831</v>
+        <v>8.020288114358037</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09634266595123495</v>
+        <v>0.09614471280001538</v>
       </c>
       <c r="C32">
-        <v>2027.651831018653</v>
+        <v>2007.180173922798</v>
       </c>
       <c r="D32">
-        <v>2861.471831018653</v>
+        <v>2868.794173922798</v>
       </c>
       <c r="E32">
-        <v>109.1199999999998</v>
+        <v>136.9139999999999</v>
       </c>
       <c r="F32">
-        <v>833.8199999999998</v>
+        <v>861.6139999999999</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3911,28 +3911,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M32">
-        <v>44.60936999999999</v>
+        <v>46.096349</v>
       </c>
       <c r="N32">
-        <v>313.1706299999999</v>
+        <v>311.6836509999999</v>
       </c>
       <c r="O32">
-        <v>78.29265749999998</v>
+        <v>77.92091274999999</v>
       </c>
       <c r="P32">
-        <v>234.8779724999999</v>
+        <v>233.76273825</v>
       </c>
       <c r="Q32">
-        <v>238.5979724999999</v>
+        <v>237.48273825</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1204359513589071</v>
+        <v>0.1213129895652397</v>
       </c>
       <c r="T32">
-        <v>1.454793611808309</v>
+        <v>1.471888718880087</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.020288114358037</v>
+        <v>7.761569142927132</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09614471280001538</v>
+        <v>0.09613875964879584</v>
       </c>
       <c r="C33">
-        <v>2007.180173922798</v>
+        <v>1979.606963158479</v>
       </c>
       <c r="D33">
-        <v>2868.794173922798</v>
+        <v>2869.014963158479</v>
       </c>
       <c r="E33">
-        <v>136.9139999999999</v>
+        <v>164.7079999999999</v>
       </c>
       <c r="F33">
-        <v>861.6139999999999</v>
+        <v>889.4079999999999</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3993,45 +3993,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M33">
-        <v>46.096349</v>
+        <v>48.2948544</v>
       </c>
       <c r="N33">
-        <v>311.6836509999999</v>
+        <v>309.4851455999999</v>
       </c>
       <c r="O33">
-        <v>77.92091274999999</v>
+        <v>77.37128639999997</v>
       </c>
       <c r="P33">
-        <v>233.76273825</v>
+        <v>232.1138591999999</v>
       </c>
       <c r="Q33">
-        <v>237.48273825</v>
+        <v>235.8338591999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1213129895652397</v>
+        <v>0.1222158230129351</v>
       </c>
       <c r="T33">
-        <v>1.471888718880087</v>
+        <v>1.489486623218683</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.761569142927132</v>
+        <v>7.408242647067591</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09613875964879584</v>
+        <v>0.09594680649757627</v>
       </c>
       <c r="C34">
-        <v>1979.606963158479</v>
+        <v>1958.950341574237</v>
       </c>
       <c r="D34">
-        <v>2869.014963158479</v>
+        <v>2876.152341574237</v>
       </c>
       <c r="E34">
-        <v>164.7079999999999</v>
+        <v>192.5019999999998</v>
       </c>
       <c r="F34">
-        <v>889.4079999999999</v>
+        <v>917.2019999999999</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4075,28 +4075,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M34">
-        <v>48.2948544</v>
+        <v>49.80406859999999</v>
       </c>
       <c r="N34">
-        <v>309.4851455999999</v>
+        <v>307.9759313999999</v>
       </c>
       <c r="O34">
-        <v>77.37128639999997</v>
+        <v>76.99398284999998</v>
       </c>
       <c r="P34">
-        <v>232.1138591999999</v>
+        <v>230.9819485499999</v>
       </c>
       <c r="Q34">
-        <v>235.8338591999999</v>
+        <v>234.7019485499999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1222158230129351</v>
+        <v>0.1231456067128004</v>
       </c>
       <c r="T34">
-        <v>1.489486623218683</v>
+        <v>1.507609838134549</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.408242647067591</v>
+        <v>7.183750445641301</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09594680649757627</v>
+        <v>0.09575485334635672</v>
       </c>
       <c r="C35">
-        <v>1958.950341574237</v>
+        <v>1938.329320513875</v>
       </c>
       <c r="D35">
-        <v>2876.152341574237</v>
+        <v>2883.325320513875</v>
       </c>
       <c r="E35">
-        <v>192.5019999999998</v>
+        <v>220.2959999999999</v>
       </c>
       <c r="F35">
-        <v>917.2019999999999</v>
+        <v>944.996</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4157,28 +4157,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M35">
-        <v>49.80406859999999</v>
+        <v>51.3132828</v>
       </c>
       <c r="N35">
-        <v>307.9759313999999</v>
+        <v>306.4667171999999</v>
       </c>
       <c r="O35">
-        <v>76.99398284999998</v>
+        <v>76.61667929999997</v>
       </c>
       <c r="P35">
-        <v>230.9819485499999</v>
+        <v>229.8500378999999</v>
       </c>
       <c r="Q35">
-        <v>234.7019485499999</v>
+        <v>233.5700378999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1231456067128004</v>
+        <v>0.1241035656762981</v>
       </c>
       <c r="T35">
-        <v>1.507609838134549</v>
+        <v>1.526282241381199</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.183750445641301</v>
+        <v>6.972463667828321</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09575485334635672</v>
+        <v>0.09556290019513718</v>
       </c>
       <c r="C36">
-        <v>1938.329320513875</v>
+        <v>1917.744167001073</v>
       </c>
       <c r="D36">
-        <v>2883.325320513875</v>
+        <v>2890.534167001073</v>
       </c>
       <c r="E36">
-        <v>220.2959999999999</v>
+        <v>248.0899999999999</v>
       </c>
       <c r="F36">
-        <v>944.996</v>
+        <v>972.79</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4239,28 +4239,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M36">
-        <v>51.3132828</v>
+        <v>52.822497</v>
       </c>
       <c r="N36">
-        <v>306.4667171999999</v>
+        <v>304.9575029999999</v>
       </c>
       <c r="O36">
-        <v>76.61667929999997</v>
+        <v>76.23937574999998</v>
       </c>
       <c r="P36">
-        <v>229.8500378999999</v>
+        <v>228.71812725</v>
       </c>
       <c r="Q36">
-        <v>233.5700378999999</v>
+        <v>232.43812725</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1241035656762981</v>
+        <v>0.1250910003002111</v>
       </c>
       <c r="T36">
-        <v>1.526282241381199</v>
+        <v>1.545529180112362</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.972463667828321</v>
+        <v>6.773250420176084</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09556290019513718</v>
+        <v>0.0953709470439176</v>
       </c>
       <c r="C37">
-        <v>1917.744167001073</v>
+        <v>1897.195150736637</v>
       </c>
       <c r="D37">
-        <v>2890.534167001073</v>
+        <v>2897.779150736637</v>
       </c>
       <c r="E37">
-        <v>248.0899999999999</v>
+        <v>275.8839999999999</v>
       </c>
       <c r="F37">
-        <v>972.79</v>
+        <v>1000.584</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4321,28 +4321,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M37">
-        <v>52.822497</v>
+        <v>54.3317112</v>
       </c>
       <c r="N37">
-        <v>304.9575029999999</v>
+        <v>303.4482887999999</v>
       </c>
       <c r="O37">
-        <v>76.23937574999998</v>
+        <v>75.86207219999997</v>
       </c>
       <c r="P37">
-        <v>228.71812725</v>
+        <v>227.5862165999999</v>
       </c>
       <c r="Q37">
-        <v>232.43812725</v>
+        <v>231.3062165999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1250910003002111</v>
+        <v>0.1261092922561213</v>
       </c>
       <c r="T37">
-        <v>1.545529180112362</v>
+        <v>1.565377585678873</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.773250420176084</v>
+        <v>6.585104575171192</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09537094704391762</v>
+        <v>0.09517899389269807</v>
       </c>
       <c r="C38">
-        <v>1897.195150736636</v>
+        <v>1876.682544132135</v>
       </c>
       <c r="D38">
-        <v>2897.779150736636</v>
+        <v>2905.060544132135</v>
       </c>
       <c r="E38">
-        <v>275.8839999999998</v>
+        <v>303.6779999999999</v>
       </c>
       <c r="F38">
-        <v>1000.584</v>
+        <v>1028.378</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4403,28 +4403,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M38">
-        <v>54.33171119999999</v>
+        <v>55.8409254</v>
       </c>
       <c r="N38">
-        <v>303.4482887999999</v>
+        <v>301.9390745999999</v>
       </c>
       <c r="O38">
-        <v>75.86207219999999</v>
+        <v>75.48476864999998</v>
       </c>
       <c r="P38">
-        <v>227.5862165999999</v>
+        <v>226.4543059499999</v>
       </c>
       <c r="Q38">
-        <v>231.3062165999999</v>
+        <v>230.1743059499999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1261092922561213</v>
+        <v>0.1271599109407906</v>
       </c>
       <c r="T38">
-        <v>1.565377585678873</v>
+        <v>1.585856099358607</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.585104575171194</v>
+        <v>6.407128775842241</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09517899389269807</v>
+        <v>0.09498704074147851</v>
       </c>
       <c r="C39">
-        <v>1876.682544132135</v>
+        <v>1856.206622344044</v>
       </c>
       <c r="D39">
-        <v>2905.060544132135</v>
+        <v>2912.378622344044</v>
       </c>
       <c r="E39">
-        <v>303.6779999999999</v>
+        <v>331.4719999999998</v>
       </c>
       <c r="F39">
-        <v>1028.378</v>
+        <v>1056.172</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4485,28 +4485,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M39">
-        <v>55.8409254</v>
+        <v>57.35013959999999</v>
       </c>
       <c r="N39">
-        <v>301.9390745999999</v>
+        <v>300.4298603999999</v>
       </c>
       <c r="O39">
-        <v>75.48476864999998</v>
+        <v>75.10746509999998</v>
       </c>
       <c r="P39">
-        <v>226.4543059499999</v>
+        <v>225.3223953</v>
       </c>
       <c r="Q39">
-        <v>230.1743059499999</v>
+        <v>229.0423953</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1271599109407906</v>
+        <v>0.1282444205507718</v>
       </c>
       <c r="T39">
-        <v>1.585856099358607</v>
+        <v>1.606995210253817</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.407128775842241</v>
+        <v>6.238520123846394</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09498704074147851</v>
+        <v>0.09508758759025895</v>
       </c>
       <c r="C40">
-        <v>1856.206622344044</v>
+        <v>1824.5747526087</v>
       </c>
       <c r="D40">
-        <v>2912.378622344044</v>
+        <v>2908.5407526087</v>
       </c>
       <c r="E40">
-        <v>331.4719999999998</v>
+        <v>359.2659999999998</v>
       </c>
       <c r="F40">
-        <v>1056.172</v>
+        <v>1083.966</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4567,45 +4567,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M40">
-        <v>57.35013959999999</v>
+        <v>59.9433198</v>
       </c>
       <c r="N40">
-        <v>300.4298603999999</v>
+        <v>297.8366801999999</v>
       </c>
       <c r="O40">
-        <v>75.10746509999998</v>
+        <v>74.45917004999998</v>
       </c>
       <c r="P40">
-        <v>225.3223953</v>
+        <v>223.3775101499999</v>
       </c>
       <c r="Q40">
-        <v>229.0423953</v>
+        <v>227.0975101499999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1282444205507718</v>
+        <v>0.1293644878528835</v>
       </c>
       <c r="T40">
-        <v>1.606995210253817</v>
+        <v>1.628827406752148</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.238520123846394</v>
+        <v>5.968638393631311</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09508758759025895</v>
+        <v>0.09490313443903942</v>
       </c>
       <c r="C41">
-        <v>1824.5747526087</v>
+        <v>1803.829084177728</v>
       </c>
       <c r="D41">
-        <v>2908.5407526087</v>
+        <v>2915.589084177728</v>
       </c>
       <c r="E41">
-        <v>359.2659999999998</v>
+        <v>387.0599999999999</v>
       </c>
       <c r="F41">
-        <v>1083.966</v>
+        <v>1111.76</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4649,28 +4649,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M41">
-        <v>59.9433198</v>
+        <v>61.480328</v>
       </c>
       <c r="N41">
-        <v>297.8366801999999</v>
+        <v>296.2996719999999</v>
       </c>
       <c r="O41">
-        <v>74.45917004999998</v>
+        <v>74.07491799999998</v>
       </c>
       <c r="P41">
-        <v>223.3775101499999</v>
+        <v>222.224754</v>
       </c>
       <c r="Q41">
-        <v>227.0975101499999</v>
+        <v>225.944754</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1293644878528835</v>
+        <v>0.1305218907317323</v>
       </c>
       <c r="T41">
-        <v>1.628827406752148</v>
+        <v>1.651387343133757</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.968638393631311</v>
+        <v>5.819422433790527</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09490313443903942</v>
+        <v>0.09471868128781984</v>
       </c>
       <c r="C42">
-        <v>1803.829084177728</v>
+        <v>1783.117659488046</v>
       </c>
       <c r="D42">
-        <v>2915.589084177728</v>
+        <v>2922.671659488046</v>
       </c>
       <c r="E42">
-        <v>387.0599999999999</v>
+        <v>414.8539999999998</v>
       </c>
       <c r="F42">
-        <v>1111.76</v>
+        <v>1139.554</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4731,28 +4731,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M42">
-        <v>61.480328</v>
+        <v>63.0173362</v>
       </c>
       <c r="N42">
-        <v>296.2996719999999</v>
+        <v>294.7626637999999</v>
       </c>
       <c r="O42">
-        <v>74.07491799999998</v>
+        <v>73.69066594999998</v>
       </c>
       <c r="P42">
-        <v>222.224754</v>
+        <v>221.0719978499999</v>
       </c>
       <c r="Q42">
-        <v>225.944754</v>
+        <v>224.7919978499999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1305218907317323</v>
+        <v>0.1317185276064743</v>
       </c>
       <c r="T42">
-        <v>1.651387343133757</v>
+        <v>1.674712023121522</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.819422433790527</v>
+        <v>5.677485301259051</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09471868128781984</v>
+        <v>0.0945342281366003</v>
       </c>
       <c r="C43">
-        <v>1783.117659488046</v>
+        <v>1762.440728702964</v>
       </c>
       <c r="D43">
-        <v>2922.671659488046</v>
+        <v>2929.788728702964</v>
       </c>
       <c r="E43">
-        <v>414.8539999999998</v>
+        <v>442.6479999999999</v>
       </c>
       <c r="F43">
-        <v>1139.554</v>
+        <v>1167.348</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4813,28 +4813,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M43">
-        <v>63.0173362</v>
+        <v>64.55434440000001</v>
       </c>
       <c r="N43">
-        <v>294.7626637999999</v>
+        <v>293.2256555999999</v>
       </c>
       <c r="O43">
-        <v>73.69066594999998</v>
+        <v>73.30641389999998</v>
       </c>
       <c r="P43">
-        <v>221.0719978499999</v>
+        <v>219.9192416999999</v>
       </c>
       <c r="Q43">
-        <v>224.7919978499999</v>
+        <v>223.6392416999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1317185276064743</v>
+        <v>0.1329564278217246</v>
       </c>
       <c r="T43">
-        <v>1.674712023121522</v>
+        <v>1.698841002419209</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.677485301259051</v>
+        <v>5.542307079800502</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09453422813660031</v>
+        <v>0.09434977498538075</v>
       </c>
       <c r="C44">
-        <v>1762.440728702963</v>
+        <v>1741.798544428464</v>
       </c>
       <c r="D44">
-        <v>2929.788728702963</v>
+        <v>2936.940544428464</v>
       </c>
       <c r="E44">
-        <v>442.6479999999997</v>
+        <v>470.4419999999998</v>
       </c>
       <c r="F44">
-        <v>1167.348</v>
+        <v>1195.142</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4895,28 +4895,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M44">
-        <v>64.55434439999999</v>
+        <v>66.09135259999999</v>
       </c>
       <c r="N44">
-        <v>293.2256555999999</v>
+        <v>291.6886473999999</v>
       </c>
       <c r="O44">
-        <v>73.30641389999998</v>
+        <v>72.92216184999998</v>
       </c>
       <c r="P44">
-        <v>219.9192416999999</v>
+        <v>218.7664855499999</v>
       </c>
       <c r="Q44">
-        <v>223.6392416999999</v>
+        <v>222.4864855499999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1329564278217246</v>
+        <v>0.1342377631322469</v>
       </c>
       <c r="T44">
-        <v>1.698841002419209</v>
+        <v>1.723816612569447</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.542307079800503</v>
+        <v>5.413416217479561</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09434977498538075</v>
+        <v>0.09416532183416121</v>
       </c>
       <c r="C45">
-        <v>1741.798544428464</v>
+        <v>1721.191361743072</v>
       </c>
       <c r="D45">
-        <v>2936.940544428464</v>
+        <v>2944.127361743072</v>
       </c>
       <c r="E45">
-        <v>470.4419999999998</v>
+        <v>498.2359999999999</v>
       </c>
       <c r="F45">
-        <v>1195.142</v>
+        <v>1222.936</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4977,28 +4977,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M45">
-        <v>66.09135259999999</v>
+        <v>67.6283608</v>
       </c>
       <c r="N45">
-        <v>291.6886473999999</v>
+        <v>290.1516391999999</v>
       </c>
       <c r="O45">
-        <v>72.92216184999998</v>
+        <v>72.53790979999998</v>
       </c>
       <c r="P45">
-        <v>218.7664855499999</v>
+        <v>217.6137294</v>
       </c>
       <c r="Q45">
-        <v>222.4864855499999</v>
+        <v>221.3337294</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1342377631322469</v>
+        <v>0.135564860418145</v>
       </c>
       <c r="T45">
-        <v>1.723816612569447</v>
+        <v>1.74968420879648</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.413416217479561</v>
+        <v>5.290384030718662</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09416532183416121</v>
+        <v>0.09398086868294164</v>
       </c>
       <c r="C46">
-        <v>1721.191361743072</v>
+        <v>1700.619438228195</v>
       </c>
       <c r="D46">
-        <v>2944.127361743072</v>
+        <v>2951.349438228195</v>
       </c>
       <c r="E46">
-        <v>498.2359999999999</v>
+        <v>526.0299999999997</v>
       </c>
       <c r="F46">
-        <v>1222.936</v>
+        <v>1250.73</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5059,28 +5059,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M46">
-        <v>67.6283608</v>
+        <v>69.16536899999998</v>
       </c>
       <c r="N46">
-        <v>290.1516391999999</v>
+        <v>288.6146309999999</v>
       </c>
       <c r="O46">
-        <v>72.53790979999998</v>
+        <v>72.15365774999998</v>
       </c>
       <c r="P46">
-        <v>217.6137294</v>
+        <v>216.4609732499999</v>
       </c>
       <c r="Q46">
-        <v>221.3337294</v>
+        <v>220.1809732499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.135564860418145</v>
+        <v>0.1369402157871666</v>
       </c>
       <c r="T46">
-        <v>1.74968420879648</v>
+        <v>1.776492444886314</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.290384030718662</v>
+        <v>5.172819941147137</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09398086868294164</v>
+        <v>0.09379641553172208</v>
       </c>
       <c r="C47">
-        <v>1700.619438228195</v>
+        <v>1680.083033998886</v>
       </c>
       <c r="D47">
-        <v>2951.349438228195</v>
+        <v>2958.607033998886</v>
       </c>
       <c r="E47">
-        <v>526.0299999999997</v>
+        <v>553.8239999999998</v>
       </c>
       <c r="F47">
-        <v>1250.73</v>
+        <v>1278.524</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5141,28 +5141,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M47">
-        <v>69.16536899999998</v>
+        <v>70.7023772</v>
       </c>
       <c r="N47">
-        <v>288.6146309999999</v>
+        <v>287.0776227999999</v>
       </c>
       <c r="O47">
-        <v>72.15365774999998</v>
+        <v>71.76940569999998</v>
       </c>
       <c r="P47">
-        <v>216.4609732499999</v>
+        <v>215.3082170999999</v>
       </c>
       <c r="Q47">
-        <v>220.1809732499999</v>
+        <v>219.0282170999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1369402157871666</v>
+        <v>0.1383665102439298</v>
       </c>
       <c r="T47">
-        <v>1.776492444886314</v>
+        <v>1.804293578609104</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.172819941147137</v>
+        <v>5.060367333730894</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09379641553172208</v>
+        <v>0.09361196238050253</v>
       </c>
       <c r="C48">
-        <v>1680.083033998886</v>
+        <v>1659.582411735079</v>
       </c>
       <c r="D48">
-        <v>2958.607033998886</v>
+        <v>2965.900411735079</v>
       </c>
       <c r="E48">
-        <v>553.8239999999998</v>
+        <v>581.6179999999999</v>
       </c>
       <c r="F48">
-        <v>1278.524</v>
+        <v>1306.318</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5223,28 +5223,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M48">
-        <v>70.7023772</v>
+        <v>72.2393854</v>
       </c>
       <c r="N48">
-        <v>287.0776227999999</v>
+        <v>285.5406145999999</v>
       </c>
       <c r="O48">
-        <v>71.76940569999998</v>
+        <v>71.38515364999998</v>
       </c>
       <c r="P48">
-        <v>215.3082170999999</v>
+        <v>214.1554609499999</v>
       </c>
       <c r="Q48">
-        <v>219.0282170999999</v>
+        <v>217.8754609499999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1383665102439298</v>
+        <v>0.1398466271330236</v>
       </c>
       <c r="T48">
-        <v>1.804293578609104</v>
+        <v>1.83314381171766</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.060367333730894</v>
+        <v>4.952699943651512</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09361196238050253</v>
+        <v>0.09342750922928297</v>
       </c>
       <c r="C49">
-        <v>1659.582411735079</v>
+        <v>1639.117836713278</v>
       </c>
       <c r="D49">
-        <v>2965.900411735079</v>
+        <v>2973.229836713278</v>
       </c>
       <c r="E49">
-        <v>581.6179999999999</v>
+        <v>609.4119999999998</v>
       </c>
       <c r="F49">
-        <v>1306.318</v>
+        <v>1334.112</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5305,28 +5305,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M49">
-        <v>72.2393854</v>
+        <v>73.77639359999999</v>
       </c>
       <c r="N49">
-        <v>285.5406145999999</v>
+        <v>284.0036063999999</v>
       </c>
       <c r="O49">
-        <v>71.38515364999998</v>
+        <v>71.00090159999998</v>
       </c>
       <c r="P49">
-        <v>214.1554609499999</v>
+        <v>213.0027047999999</v>
       </c>
       <c r="Q49">
-        <v>217.8754609499999</v>
+        <v>216.7227047999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1398466271330236</v>
+        <v>0.1413836715947749</v>
       </c>
       <c r="T49">
-        <v>1.83314381171766</v>
+        <v>1.863103669176546</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.952699943651512</v>
+        <v>4.84951869482544</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09342750922928297</v>
+        <v>0.09324305607806342</v>
       </c>
       <c r="C50">
-        <v>1639.117836713278</v>
+        <v>1618.689576838724</v>
       </c>
       <c r="D50">
-        <v>2973.229836713278</v>
+        <v>2980.595576838723</v>
       </c>
       <c r="E50">
-        <v>609.4119999999998</v>
+        <v>637.2059999999997</v>
       </c>
       <c r="F50">
-        <v>1334.112</v>
+        <v>1361.906</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5387,28 +5387,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M50">
-        <v>73.77639359999999</v>
+        <v>75.31340179999999</v>
       </c>
       <c r="N50">
-        <v>284.0036063999999</v>
+        <v>282.4665981999999</v>
       </c>
       <c r="O50">
-        <v>71.00090159999998</v>
+        <v>70.61664954999998</v>
       </c>
       <c r="P50">
-        <v>213.0027047999999</v>
+        <v>211.8499486499999</v>
       </c>
       <c r="Q50">
-        <v>216.7227047999999</v>
+        <v>215.5699486499999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1413836715947749</v>
+        <v>0.1429809923099283</v>
       </c>
       <c r="T50">
-        <v>1.863103669176546</v>
+        <v>1.894238423006368</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.84951869482544</v>
+        <v>4.750548925543288</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09324305607806342</v>
+        <v>0.09305860292684387</v>
       </c>
       <c r="C51">
-        <v>1618.689576838724</v>
+        <v>1598.297902678031</v>
       </c>
       <c r="D51">
-        <v>2980.595576838723</v>
+        <v>2987.997902678031</v>
       </c>
       <c r="E51">
-        <v>637.2059999999997</v>
+        <v>664.9999999999998</v>
       </c>
       <c r="F51">
-        <v>1361.906</v>
+        <v>1389.7</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M51">
-        <v>75.31340179999999</v>
+        <v>76.85041</v>
       </c>
       <c r="N51">
-        <v>282.4665981999999</v>
+        <v>280.9295899999999</v>
       </c>
       <c r="O51">
-        <v>70.61664954999998</v>
+        <v>70.23239749999998</v>
       </c>
       <c r="P51">
-        <v>211.8499486499999</v>
+        <v>210.6971924999999</v>
       </c>
       <c r="Q51">
-        <v>215.5699486499999</v>
+        <v>214.4171924999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1429809923099283</v>
+        <v>0.1446422058536877</v>
       </c>
       <c r="T51">
-        <v>1.894238423006368</v>
+        <v>1.926618566989383</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.750548925543288</v>
+        <v>4.655537947032422</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09305860292684387</v>
+        <v>0.0928741497756243</v>
       </c>
       <c r="C52">
-        <v>1598.297902678031</v>
+        <v>1577.943087492324</v>
       </c>
       <c r="D52">
-        <v>2987.997902678031</v>
+        <v>2995.437087492324</v>
       </c>
       <c r="E52">
-        <v>664.9999999999998</v>
+        <v>692.7939999999999</v>
       </c>
       <c r="F52">
-        <v>1389.7</v>
+        <v>1417.494</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5551,28 +5551,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M52">
-        <v>76.85041</v>
+        <v>78.3874182</v>
       </c>
       <c r="N52">
-        <v>280.9295899999999</v>
+        <v>279.3925817999999</v>
       </c>
       <c r="O52">
-        <v>70.23239749999998</v>
+        <v>69.84814544999998</v>
       </c>
       <c r="P52">
-        <v>210.6971924999999</v>
+        <v>209.5444363499999</v>
       </c>
       <c r="Q52">
-        <v>214.4171924999999</v>
+        <v>213.2644363499999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1446422058536877</v>
+        <v>0.1463712240318863</v>
       </c>
       <c r="T52">
-        <v>1.926618566989383</v>
+        <v>1.960320349502317</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.655537947032422</v>
+        <v>4.564252889247472</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0928741497756243</v>
+        <v>0.09366469662440477</v>
       </c>
       <c r="C53">
-        <v>1577.943087492324</v>
+        <v>1518.523603072826</v>
       </c>
       <c r="D53">
-        <v>2995.437087492324</v>
+        <v>2963.811603072826</v>
       </c>
       <c r="E53">
-        <v>692.7939999999999</v>
+        <v>720.5879999999997</v>
       </c>
       <c r="F53">
-        <v>1417.494</v>
+        <v>1445.288</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5633,45 +5633,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M53">
-        <v>78.3874182</v>
+        <v>83.5376464</v>
       </c>
       <c r="N53">
-        <v>279.3925817999999</v>
+        <v>274.2423535999999</v>
       </c>
       <c r="O53">
-        <v>69.84814544999998</v>
+        <v>68.56058839999997</v>
       </c>
       <c r="P53">
-        <v>209.5444363499999</v>
+        <v>205.6817651999999</v>
       </c>
       <c r="Q53">
-        <v>213.2644363499999</v>
+        <v>209.4017651999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1463712240318863</v>
+        <v>0.1481722846341766</v>
       </c>
       <c r="T53">
-        <v>1.960320349502317</v>
+        <v>1.995426372953289</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.564252889247472</v>
+        <v>4.282859470170564</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09366469662440477</v>
+        <v>0.09349899347318519</v>
       </c>
       <c r="C54">
-        <v>1518.523603072826</v>
+        <v>1497.30304589107</v>
       </c>
       <c r="D54">
-        <v>2963.811603072826</v>
+        <v>2970.38504589107</v>
       </c>
       <c r="E54">
-        <v>720.5879999999997</v>
+        <v>748.3819999999998</v>
       </c>
       <c r="F54">
-        <v>1445.288</v>
+        <v>1473.082</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5715,28 +5715,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M54">
-        <v>83.5376464</v>
+        <v>85.1441396</v>
       </c>
       <c r="N54">
-        <v>274.2423535999999</v>
+        <v>272.6358603999999</v>
       </c>
       <c r="O54">
-        <v>68.56058839999997</v>
+        <v>68.15896509999997</v>
       </c>
       <c r="P54">
-        <v>205.6817651999999</v>
+        <v>204.4768952999999</v>
       </c>
       <c r="Q54">
-        <v>209.4017651999999</v>
+        <v>208.1968952999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1481722846341766</v>
+        <v>0.15004998611316</v>
       </c>
       <c r="T54">
-        <v>1.995426372953289</v>
+        <v>2.032026269742601</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.282859470170564</v>
+        <v>4.202050800922063</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09349899347318519</v>
+        <v>0.09333329032196563</v>
       </c>
       <c r="C55">
-        <v>1497.30304589107</v>
+        <v>1476.111712023867</v>
       </c>
       <c r="D55">
-        <v>2970.38504589107</v>
+        <v>2976.987712023867</v>
       </c>
       <c r="E55">
-        <v>748.3819999999998</v>
+        <v>776.1759999999999</v>
       </c>
       <c r="F55">
-        <v>1473.082</v>
+        <v>1500.876</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5797,28 +5797,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M55">
-        <v>85.1441396</v>
+        <v>86.75063280000001</v>
       </c>
       <c r="N55">
-        <v>272.6358603999999</v>
+        <v>271.0293671999999</v>
       </c>
       <c r="O55">
-        <v>68.15896509999997</v>
+        <v>67.75734179999998</v>
       </c>
       <c r="P55">
-        <v>204.4768952999999</v>
+        <v>203.2720253999999</v>
       </c>
       <c r="Q55">
-        <v>208.1968952999999</v>
+        <v>206.9920253999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.15004998611316</v>
+        <v>0.1520093267868818</v>
       </c>
       <c r="T55">
-        <v>2.032026269742601</v>
+        <v>2.070217466392318</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.202050800922063</v>
+        <v>4.124235045349431</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09333329032196563</v>
+        <v>0.09316758717074609</v>
       </c>
       <c r="C56">
-        <v>1476.111712023867</v>
+        <v>1454.949796780892</v>
       </c>
       <c r="D56">
-        <v>2976.987712023867</v>
+        <v>2983.619796780892</v>
       </c>
       <c r="E56">
-        <v>776.1759999999999</v>
+        <v>803.9699999999998</v>
       </c>
       <c r="F56">
-        <v>1500.876</v>
+        <v>1528.67</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5879,28 +5879,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M56">
-        <v>86.75063280000001</v>
+        <v>88.35712599999999</v>
       </c>
       <c r="N56">
-        <v>271.0293671999999</v>
+        <v>269.4228739999999</v>
       </c>
       <c r="O56">
-        <v>67.75734179999998</v>
+        <v>67.35571849999998</v>
       </c>
       <c r="P56">
-        <v>203.2720253999999</v>
+        <v>202.0671555</v>
       </c>
       <c r="Q56">
-        <v>206.9920253999999</v>
+        <v>205.7871555</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1520093267868818</v>
+        <v>0.1540557492683247</v>
       </c>
       <c r="T56">
-        <v>2.070217466392318</v>
+        <v>2.1101060495598</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.124235045349431</v>
+        <v>4.049248953615806</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09316758717074609</v>
+        <v>0.09447188401952654</v>
       </c>
       <c r="C57">
-        <v>1454.949796780892</v>
+        <v>1375.738101768292</v>
       </c>
       <c r="D57">
-        <v>2983.619796780892</v>
+        <v>2932.202101768292</v>
       </c>
       <c r="E57">
-        <v>803.9699999999998</v>
+        <v>831.7639999999999</v>
       </c>
       <c r="F57">
-        <v>1528.67</v>
+        <v>1556.464</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5961,45 +5961,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M57">
-        <v>88.35712599999999</v>
+        <v>95.4112432</v>
       </c>
       <c r="N57">
-        <v>269.4228739999999</v>
+        <v>262.3687567999999</v>
       </c>
       <c r="O57">
-        <v>67.35571849999998</v>
+        <v>65.59218919999998</v>
       </c>
       <c r="P57">
-        <v>202.0671555</v>
+        <v>196.7765675999999</v>
       </c>
       <c r="Q57">
-        <v>205.7871555</v>
+        <v>200.4965675999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1540557492683247</v>
+        <v>0.1561951909534694</v>
       </c>
       <c r="T57">
-        <v>2.1101060495598</v>
+        <v>2.151807750143986</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.049248953615806</v>
+        <v>3.749872530745936</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09447188401952654</v>
+        <v>0.09433243086830698</v>
       </c>
       <c r="C58">
-        <v>1375.738101768292</v>
+        <v>1353.356825518943</v>
       </c>
       <c r="D58">
-        <v>2932.202101768292</v>
+        <v>2937.614825518943</v>
       </c>
       <c r="E58">
-        <v>831.7639999999999</v>
+        <v>859.558</v>
       </c>
       <c r="F58">
-        <v>1556.464</v>
+        <v>1584.258</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6043,28 +6043,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M58">
-        <v>95.4112432</v>
+        <v>97.1150154</v>
       </c>
       <c r="N58">
-        <v>262.3687567999999</v>
+        <v>260.6649845999999</v>
       </c>
       <c r="O58">
-        <v>65.59218919999998</v>
+        <v>65.16624614999998</v>
       </c>
       <c r="P58">
-        <v>196.7765675999999</v>
+        <v>195.4987384499999</v>
       </c>
       <c r="Q58">
-        <v>200.4965675999999</v>
+        <v>199.2187384499999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1561951909534694</v>
+        <v>0.1584341415542023</v>
       </c>
       <c r="T58">
-        <v>2.151807750143986</v>
+        <v>2.195449064708832</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.749872530745936</v>
+        <v>3.684085293364427</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09433243086830698</v>
+        <v>0.09419297771708744</v>
       </c>
       <c r="C59">
-        <v>1353.356825518943</v>
+        <v>1330.99556955436</v>
       </c>
       <c r="D59">
-        <v>2937.614825518943</v>
+        <v>2943.04756955436</v>
       </c>
       <c r="E59">
-        <v>859.558</v>
+        <v>887.3519999999999</v>
       </c>
       <c r="F59">
-        <v>1584.258</v>
+        <v>1612.052</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6125,28 +6125,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M59">
-        <v>97.1150154</v>
+        <v>98.81878759999999</v>
       </c>
       <c r="N59">
-        <v>260.6649845999999</v>
+        <v>258.9612123999999</v>
       </c>
       <c r="O59">
-        <v>65.16624614999998</v>
+        <v>64.74030309999998</v>
       </c>
       <c r="P59">
-        <v>195.4987384499999</v>
+        <v>194.2209092999999</v>
       </c>
       <c r="Q59">
-        <v>199.2187384499999</v>
+        <v>197.9409092999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1584341415542023</v>
+        <v>0.1607797088502082</v>
       </c>
       <c r="T59">
-        <v>2.195449064708832</v>
+        <v>2.241168537110099</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.684085293364427</v>
+        <v>3.620566581409869</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09419297771708743</v>
+        <v>0.09405352456586788</v>
       </c>
       <c r="C60">
-        <v>1330.99556955436</v>
+        <v>1308.654445155236</v>
       </c>
       <c r="D60">
-        <v>2943.04756955436</v>
+        <v>2948.500445155236</v>
       </c>
       <c r="E60">
-        <v>887.3519999999996</v>
+        <v>915.1459999999997</v>
       </c>
       <c r="F60">
-        <v>1612.052</v>
+        <v>1639.846</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6207,28 +6207,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M60">
-        <v>98.81878759999998</v>
+        <v>100.5225598</v>
       </c>
       <c r="N60">
-        <v>258.9612123999999</v>
+        <v>257.2574401999999</v>
       </c>
       <c r="O60">
-        <v>64.74030309999998</v>
+        <v>64.31436004999998</v>
       </c>
       <c r="P60">
-        <v>194.2209092999999</v>
+        <v>192.9430801499999</v>
       </c>
       <c r="Q60">
-        <v>197.9409092999999</v>
+        <v>196.6630801499999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1607797088502082</v>
+        <v>0.1632396940630924</v>
       </c>
       <c r="T60">
-        <v>2.241168537110098</v>
+        <v>2.28911822767728</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.620566581409869</v>
+        <v>3.559201046131736</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09405352456586788</v>
+        <v>0.09517407141464834</v>
       </c>
       <c r="C61">
-        <v>1308.654445155236</v>
+        <v>1237.60775063386</v>
       </c>
       <c r="D61">
-        <v>2948.500445155236</v>
+        <v>2905.24775063386</v>
       </c>
       <c r="E61">
-        <v>915.1459999999997</v>
+        <v>942.9399999999996</v>
       </c>
       <c r="F61">
-        <v>1639.846</v>
+        <v>1667.64</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6289,45 +6289,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M61">
-        <v>100.5225598</v>
+        <v>106.895724</v>
       </c>
       <c r="N61">
-        <v>257.2574401999999</v>
+        <v>250.8842759999999</v>
       </c>
       <c r="O61">
-        <v>64.31436004999998</v>
+        <v>62.72106899999999</v>
       </c>
       <c r="P61">
-        <v>192.9430801499999</v>
+        <v>188.1632069999999</v>
       </c>
       <c r="Q61">
-        <v>196.6630801499999</v>
+        <v>191.8832069999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1632396940630924</v>
+        <v>0.1658226785366208</v>
       </c>
       <c r="T61">
-        <v>2.28911822767728</v>
+        <v>2.339465402772822</v>
       </c>
       <c r="U61">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.559201046131736</v>
+        <v>3.347000110126014</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09517407141464834</v>
+        <v>0.09505561826342879</v>
       </c>
       <c r="C62">
-        <v>1237.60775063386</v>
+        <v>1214.325923488352</v>
       </c>
       <c r="D62">
-        <v>2905.24775063386</v>
+        <v>2909.759923488351</v>
       </c>
       <c r="E62">
-        <v>942.9399999999996</v>
+        <v>970.7339999999997</v>
       </c>
       <c r="F62">
-        <v>1667.64</v>
+        <v>1695.434</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6371,28 +6371,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M62">
-        <v>106.895724</v>
+        <v>108.6773194</v>
       </c>
       <c r="N62">
-        <v>250.8842759999999</v>
+        <v>249.1026805999999</v>
       </c>
       <c r="O62">
-        <v>62.72106899999999</v>
+        <v>62.27567014999998</v>
       </c>
       <c r="P62">
-        <v>188.1632069999999</v>
+        <v>186.8270104499999</v>
       </c>
       <c r="Q62">
-        <v>191.8832069999999</v>
+        <v>190.5470104499999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1658226785366208</v>
+        <v>0.1685381237523815</v>
       </c>
       <c r="T62">
-        <v>2.339465402772822</v>
+        <v>2.392394484283519</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.347000110126014</v>
+        <v>3.292131255861653</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09505561826342879</v>
+        <v>0.09493716511220922</v>
       </c>
       <c r="C63">
-        <v>1214.325923488352</v>
+        <v>1191.05813395732</v>
       </c>
       <c r="D63">
-        <v>2909.759923488351</v>
+        <v>2914.28613395732</v>
       </c>
       <c r="E63">
-        <v>970.7339999999997</v>
+        <v>998.5279999999998</v>
       </c>
       <c r="F63">
-        <v>1695.434</v>
+        <v>1723.228</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6453,28 +6453,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M63">
-        <v>108.6773194</v>
+        <v>110.4589148</v>
       </c>
       <c r="N63">
-        <v>249.1026805999999</v>
+        <v>247.3210851999999</v>
       </c>
       <c r="O63">
-        <v>62.27567014999998</v>
+        <v>61.83027129999998</v>
       </c>
       <c r="P63">
-        <v>186.8270104499999</v>
+        <v>185.4908138999999</v>
       </c>
       <c r="Q63">
-        <v>190.5470104499999</v>
+        <v>189.2108138999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1685381237523815</v>
+        <v>0.1713964871373927</v>
       </c>
       <c r="T63">
-        <v>2.392394484283519</v>
+        <v>2.448109306926359</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.292131255861653</v>
+        <v>3.239032364638077</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09493716511220922</v>
+        <v>0.09481871196098966</v>
       </c>
       <c r="C64">
-        <v>1191.05813395732</v>
+        <v>1167.804447650491</v>
       </c>
       <c r="D64">
-        <v>2914.28613395732</v>
+        <v>2918.826447650491</v>
       </c>
       <c r="E64">
-        <v>998.5279999999998</v>
+        <v>1026.322</v>
       </c>
       <c r="F64">
-        <v>1723.228</v>
+        <v>1751.022</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6535,28 +6535,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M64">
-        <v>110.4589148</v>
+        <v>112.2405102</v>
       </c>
       <c r="N64">
-        <v>247.3210851999999</v>
+        <v>245.5394897999999</v>
       </c>
       <c r="O64">
-        <v>61.83027129999998</v>
+        <v>61.38487244999998</v>
       </c>
       <c r="P64">
-        <v>185.4908138999999</v>
+        <v>184.1546173499999</v>
       </c>
       <c r="Q64">
-        <v>189.2108138999999</v>
+        <v>187.8746173499999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1713964871373927</v>
+        <v>0.1744093566513234</v>
       </c>
       <c r="T64">
-        <v>2.448109306926359</v>
+        <v>2.506835741603946</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.239032364638077</v>
+        <v>3.187619152500965</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09481871196098966</v>
+        <v>0.09470025880977012</v>
       </c>
       <c r="C65">
-        <v>1167.804447650491</v>
+        <v>1144.564930587098</v>
       </c>
       <c r="D65">
-        <v>2918.826447650491</v>
+        <v>2923.380930587098</v>
       </c>
       <c r="E65">
-        <v>1026.322</v>
+        <v>1054.116</v>
       </c>
       <c r="F65">
-        <v>1751.022</v>
+        <v>1778.816</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6617,28 +6617,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M65">
-        <v>112.2405102</v>
+        <v>114.0221056</v>
       </c>
       <c r="N65">
-        <v>245.5394897999999</v>
+        <v>243.7578943999999</v>
       </c>
       <c r="O65">
-        <v>61.38487244999998</v>
+        <v>60.93947359999999</v>
       </c>
       <c r="P65">
-        <v>184.1546173499999</v>
+        <v>182.8184208</v>
       </c>
       <c r="Q65">
-        <v>187.8746173499999</v>
+        <v>186.5384208</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1744093566513234</v>
+        <v>0.177589607804917</v>
       </c>
       <c r="T65">
-        <v>2.506835741603946</v>
+        <v>2.568824755985844</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.187619152500965</v>
+        <v>3.137812603243138</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09470025880977012</v>
+        <v>0.09458180565855057</v>
       </c>
       <c r="C66">
-        <v>1144.564930587098</v>
+        <v>1121.339649199079</v>
       </c>
       <c r="D66">
-        <v>2923.380930587098</v>
+        <v>2927.949649199079</v>
       </c>
       <c r="E66">
-        <v>1054.116</v>
+        <v>1081.91</v>
       </c>
       <c r="F66">
-        <v>1778.816</v>
+        <v>1806.61</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6699,28 +6699,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M66">
-        <v>114.0221056</v>
+        <v>115.803701</v>
       </c>
       <c r="N66">
-        <v>243.7578943999999</v>
+        <v>241.9762989999999</v>
       </c>
       <c r="O66">
-        <v>60.93947359999999</v>
+        <v>60.49407474999998</v>
       </c>
       <c r="P66">
-        <v>182.8184208</v>
+        <v>181.4822242499999</v>
       </c>
       <c r="Q66">
-        <v>186.5384208</v>
+        <v>185.2022242499999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.177589607804917</v>
+        <v>0.1809515875958587</v>
       </c>
       <c r="T66">
-        <v>2.568824755985844</v>
+        <v>2.634355999760993</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.137812603243138</v>
+        <v>3.089538563193243</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09458180565855057</v>
+        <v>0.09446335250733101</v>
       </c>
       <c r="C67">
-        <v>1121.339649199079</v>
+        <v>1098.128670334305</v>
       </c>
       <c r="D67">
-        <v>2927.949649199079</v>
+        <v>2932.532670334305</v>
       </c>
       <c r="E67">
-        <v>1081.91</v>
+        <v>1109.704</v>
       </c>
       <c r="F67">
-        <v>1806.61</v>
+        <v>1834.404</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6781,28 +6781,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M67">
-        <v>115.803701</v>
+        <v>117.5852964</v>
       </c>
       <c r="N67">
-        <v>241.9762989999999</v>
+        <v>240.1947035999999</v>
       </c>
       <c r="O67">
-        <v>60.49407474999998</v>
+        <v>60.04867589999998</v>
       </c>
       <c r="P67">
-        <v>181.4822242499999</v>
+        <v>180.1460276999999</v>
       </c>
       <c r="Q67">
-        <v>185.2022242499999</v>
+        <v>183.8660276999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1809515875958587</v>
+        <v>0.1845113309039147</v>
       </c>
       <c r="T67">
-        <v>2.634355999760993</v>
+        <v>2.703742022581739</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.089538563193243</v>
+        <v>3.04272737284183</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09446335250733101</v>
+        <v>0.09826439935611145</v>
       </c>
       <c r="C68">
-        <v>1098.128670334305</v>
+        <v>930.084248858534</v>
       </c>
       <c r="D68">
-        <v>2932.532670334305</v>
+        <v>2792.282248858534</v>
       </c>
       <c r="E68">
-        <v>1109.704</v>
+        <v>1137.498</v>
       </c>
       <c r="F68">
-        <v>1834.404</v>
+        <v>1862.198</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6863,45 +6863,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M68">
-        <v>117.5852964</v>
+        <v>133.8920362</v>
       </c>
       <c r="N68">
-        <v>240.1947035999999</v>
+        <v>223.8879637999999</v>
       </c>
       <c r="O68">
-        <v>60.04867589999998</v>
+        <v>55.97199094999998</v>
       </c>
       <c r="P68">
-        <v>180.1460276999999</v>
+        <v>167.9159728499999</v>
       </c>
       <c r="Q68">
-        <v>183.8660276999999</v>
+        <v>171.6359728499999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1845113309039147</v>
+        <v>0.1882868162306408</v>
       </c>
       <c r="T68">
-        <v>2.703742022581739</v>
+        <v>2.777333258906773</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.04272737284183</v>
+        <v>2.672152953634743</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09826439935611145</v>
+        <v>0.09820444620489188</v>
       </c>
       <c r="C69">
-        <v>930.084248858534</v>
+        <v>904.398183570923</v>
       </c>
       <c r="D69">
-        <v>2792.282248858534</v>
+        <v>2794.390183570923</v>
       </c>
       <c r="E69">
-        <v>1137.498</v>
+        <v>1165.292</v>
       </c>
       <c r="F69">
-        <v>1862.198</v>
+        <v>1889.992</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6945,28 +6945,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M69">
-        <v>133.8920362</v>
+        <v>135.8904248</v>
       </c>
       <c r="N69">
-        <v>223.8879637999999</v>
+        <v>221.8895751999999</v>
       </c>
       <c r="O69">
-        <v>55.97199094999998</v>
+        <v>55.47239379999998</v>
       </c>
       <c r="P69">
-        <v>167.9159728499999</v>
+        <v>166.4171813999999</v>
       </c>
       <c r="Q69">
-        <v>171.6359728499999</v>
+        <v>170.1371813999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1882868162306408</v>
+        <v>0.1922982693902872</v>
       </c>
       <c r="T69">
-        <v>2.777333258906773</v>
+        <v>2.855523947502121</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.672152953634743</v>
+        <v>2.632856586669526</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09820444620489188</v>
+        <v>0.09814449305367234</v>
       </c>
       <c r="C70">
-        <v>904.398183570923</v>
+        <v>878.7153033092279</v>
       </c>
       <c r="D70">
-        <v>2794.390183570923</v>
+        <v>2796.501303309228</v>
       </c>
       <c r="E70">
-        <v>1165.292</v>
+        <v>1193.086</v>
       </c>
       <c r="F70">
-        <v>1889.992</v>
+        <v>1917.786</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7027,28 +7027,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M70">
-        <v>135.8904248</v>
+        <v>137.8888134</v>
       </c>
       <c r="N70">
-        <v>221.8895751999999</v>
+        <v>219.8911865999999</v>
       </c>
       <c r="O70">
-        <v>55.47239379999998</v>
+        <v>54.97279664999998</v>
       </c>
       <c r="P70">
-        <v>166.4171813999999</v>
+        <v>164.9183899499999</v>
       </c>
       <c r="Q70">
-        <v>170.1371813999999</v>
+        <v>168.6383899499999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1922982693902872</v>
+        <v>0.1965685259795882</v>
       </c>
       <c r="T70">
-        <v>2.855523947502121</v>
+        <v>2.938759196652008</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.632856586669526</v>
+        <v>2.594699244833736</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09814449305367234</v>
+        <v>0.09808453990245278</v>
       </c>
       <c r="C71">
-        <v>878.7153033092279</v>
+        <v>853.0356152976265</v>
       </c>
       <c r="D71">
-        <v>2796.501303309228</v>
+        <v>2798.615615297626</v>
       </c>
       <c r="E71">
-        <v>1193.086</v>
+        <v>1220.88</v>
       </c>
       <c r="F71">
-        <v>1917.786</v>
+        <v>1945.58</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7109,28 +7109,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M71">
-        <v>137.8888134</v>
+        <v>139.887202</v>
       </c>
       <c r="N71">
-        <v>219.8911865999999</v>
+        <v>217.8927979999999</v>
       </c>
       <c r="O71">
-        <v>54.97279664999998</v>
+        <v>54.47319949999998</v>
       </c>
       <c r="P71">
-        <v>164.9183899499999</v>
+        <v>163.4195984999999</v>
       </c>
       <c r="Q71">
-        <v>168.6383899499999</v>
+        <v>167.1395984999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1965685259795882</v>
+        <v>0.2011234663415093</v>
       </c>
       <c r="T71">
-        <v>2.938759196652008</v>
+        <v>3.027543462411888</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.594699244833736</v>
+        <v>2.557632112764682</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09808453990245278</v>
+        <v>0.09802458675123324</v>
       </c>
       <c r="C72">
-        <v>853.0356152976265</v>
+        <v>827.359126782156</v>
       </c>
       <c r="D72">
-        <v>2798.615615297626</v>
+        <v>2800.733126782156</v>
       </c>
       <c r="E72">
-        <v>1220.88</v>
+        <v>1248.674</v>
       </c>
       <c r="F72">
-        <v>1945.58</v>
+        <v>1973.374</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7191,28 +7191,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M72">
-        <v>139.887202</v>
+        <v>141.8855906</v>
       </c>
       <c r="N72">
-        <v>217.8927979999999</v>
+        <v>215.8944093999999</v>
       </c>
       <c r="O72">
-        <v>54.47319949999998</v>
+        <v>53.97360234999998</v>
       </c>
       <c r="P72">
-        <v>163.4195984999999</v>
+        <v>161.92080705</v>
       </c>
       <c r="Q72">
-        <v>167.1395984999999</v>
+        <v>165.6408070499999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2011234663415093</v>
+        <v>0.205992540521494</v>
       </c>
       <c r="T72">
-        <v>3.027543462411888</v>
+        <v>3.122450780982794</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.557632112764682</v>
+        <v>2.521609125260954</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09802458675123324</v>
+        <v>0.1000706336000137</v>
       </c>
       <c r="C73">
-        <v>827.3591267821564</v>
+        <v>729.0656498299322</v>
       </c>
       <c r="D73">
-        <v>2800.733126782156</v>
+        <v>2730.233649829932</v>
       </c>
       <c r="E73">
-        <v>1248.674</v>
+        <v>1276.468</v>
       </c>
       <c r="F73">
-        <v>1973.374</v>
+        <v>2001.168</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7273,45 +7273,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M73">
-        <v>141.8855906</v>
+        <v>151.6885344</v>
       </c>
       <c r="N73">
-        <v>215.8944093999999</v>
+        <v>206.0914655999999</v>
       </c>
       <c r="O73">
-        <v>53.97360234999999</v>
+        <v>51.52286639999998</v>
       </c>
       <c r="P73">
-        <v>161.92080705</v>
+        <v>154.5685991999999</v>
       </c>
       <c r="Q73">
-        <v>165.6408070499999</v>
+        <v>158.2885991999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2059925405214939</v>
+        <v>0.2112094057143346</v>
       </c>
       <c r="T73">
-        <v>3.122450780982793</v>
+        <v>3.224137193737334</v>
       </c>
       <c r="U73">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.521609125260955</v>
+        <v>2.358648934246674</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1000706336000137</v>
+        <v>0.1000399304487941</v>
       </c>
       <c r="C74">
-        <v>729.0656498299322</v>
+        <v>702.303330840158</v>
       </c>
       <c r="D74">
-        <v>2730.233649829932</v>
+        <v>2731.265330840158</v>
       </c>
       <c r="E74">
-        <v>1276.468</v>
+        <v>1304.262</v>
       </c>
       <c r="F74">
-        <v>2001.168</v>
+        <v>2028.962</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7355,28 +7355,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M74">
-        <v>151.6885344</v>
+        <v>153.7953196</v>
       </c>
       <c r="N74">
-        <v>206.0914655999999</v>
+        <v>203.9846803999999</v>
       </c>
       <c r="O74">
-        <v>51.52286639999998</v>
+        <v>50.99617009999998</v>
       </c>
       <c r="P74">
-        <v>154.5685991999999</v>
+        <v>152.9885102999999</v>
       </c>
       <c r="Q74">
-        <v>158.2885991999999</v>
+        <v>156.7085102999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2112094057143346</v>
+        <v>0.2168127053659042</v>
       </c>
       <c r="T74">
-        <v>3.224137193737334</v>
+        <v>3.333355933362582</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.358648934246674</v>
+        <v>2.326338674873432</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1000399304487941</v>
+        <v>0.1000092272975746</v>
       </c>
       <c r="C75">
-        <v>702.303330840158</v>
+        <v>675.5417918334851</v>
       </c>
       <c r="D75">
-        <v>2731.265330840158</v>
+        <v>2732.297791833485</v>
       </c>
       <c r="E75">
-        <v>1304.262</v>
+        <v>1332.056</v>
       </c>
       <c r="F75">
-        <v>2028.962</v>
+        <v>2056.756</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7437,28 +7437,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M75">
-        <v>153.7953196</v>
+        <v>155.9021048</v>
       </c>
       <c r="N75">
-        <v>203.9846803999999</v>
+        <v>201.8778951999999</v>
       </c>
       <c r="O75">
-        <v>50.99617009999998</v>
+        <v>50.46947379999998</v>
       </c>
       <c r="P75">
-        <v>152.9885102999999</v>
+        <v>151.4084214</v>
       </c>
       <c r="Q75">
-        <v>156.7085102999999</v>
+        <v>155.1284214</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2168127053659042</v>
+        <v>0.2228470280675945</v>
       </c>
       <c r="T75">
-        <v>3.333355933362582</v>
+        <v>3.450976114497465</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.326338674873432</v>
+        <v>2.294901665753521</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1000092272975746</v>
+        <v>0.09997852414635502</v>
       </c>
       <c r="C76">
-        <v>675.5417918334851</v>
+        <v>648.7810336947841</v>
       </c>
       <c r="D76">
-        <v>2732.297791833485</v>
+        <v>2733.331033694784</v>
       </c>
       <c r="E76">
-        <v>1332.056</v>
+        <v>1359.85</v>
       </c>
       <c r="F76">
-        <v>2056.756</v>
+        <v>2084.55</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7519,28 +7519,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M76">
-        <v>155.9021048</v>
+        <v>158.00889</v>
       </c>
       <c r="N76">
-        <v>201.8778951999999</v>
+        <v>199.7711099999999</v>
       </c>
       <c r="O76">
-        <v>50.46947379999998</v>
+        <v>49.94277749999998</v>
       </c>
       <c r="P76">
-        <v>151.4084214</v>
+        <v>149.8283325</v>
       </c>
       <c r="Q76">
-        <v>155.1284214</v>
+        <v>153.5483325</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2228470280675945</v>
+        <v>0.2293640965854201</v>
       </c>
       <c r="T76">
-        <v>3.450976114497465</v>
+        <v>3.578005910123139</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.294901665753521</v>
+        <v>2.264302976876807</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09997852414635502</v>
+        <v>0.09994782099513547</v>
       </c>
       <c r="C77">
-        <v>648.7810336947841</v>
+        <v>622.0210573102668</v>
       </c>
       <c r="D77">
-        <v>2733.331033694784</v>
+        <v>2734.365057310266</v>
       </c>
       <c r="E77">
-        <v>1359.85</v>
+        <v>1387.644</v>
       </c>
       <c r="F77">
-        <v>2084.55</v>
+        <v>2112.344</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7601,28 +7601,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M77">
-        <v>158.00889</v>
+        <v>160.1156752</v>
       </c>
       <c r="N77">
-        <v>199.7711099999999</v>
+        <v>197.6643247999999</v>
       </c>
       <c r="O77">
-        <v>49.94277749999998</v>
+        <v>49.41608119999999</v>
       </c>
       <c r="P77">
-        <v>149.8283325</v>
+        <v>148.2482436</v>
       </c>
       <c r="Q77">
-        <v>153.5483325</v>
+        <v>151.9682436</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2293640965854201</v>
+        <v>0.2364242541463978</v>
       </c>
       <c r="T77">
-        <v>3.578005910123139</v>
+        <v>3.715621522050952</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.264302976876807</v>
+        <v>2.234509516654744</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09994782099513547</v>
+        <v>0.09991711784391592</v>
       </c>
       <c r="C78">
-        <v>622.0210573102668</v>
+        <v>595.2618635674849</v>
       </c>
       <c r="D78">
-        <v>2734.365057310266</v>
+        <v>2735.399863567485</v>
       </c>
       <c r="E78">
-        <v>1387.644</v>
+        <v>1415.438</v>
       </c>
       <c r="F78">
-        <v>2112.344</v>
+        <v>2140.138</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7683,28 +7683,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M78">
-        <v>160.1156752</v>
+        <v>162.2224604</v>
       </c>
       <c r="N78">
-        <v>197.6643247999999</v>
+        <v>195.5575395999999</v>
       </c>
       <c r="O78">
-        <v>49.41608119999999</v>
+        <v>48.88938489999997</v>
       </c>
       <c r="P78">
-        <v>148.2482436</v>
+        <v>146.6681546999999</v>
       </c>
       <c r="Q78">
-        <v>151.9682436</v>
+        <v>150.3881546999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2364242541463978</v>
+        <v>0.2440983384518083</v>
       </c>
       <c r="T78">
-        <v>3.715621522050952</v>
+        <v>3.86520370892901</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.234509516654744</v>
+        <v>2.205489912542344</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09991711784391592</v>
+        <v>0.09988641469269635</v>
       </c>
       <c r="C79">
-        <v>595.2618635674849</v>
+        <v>568.5034533553362</v>
       </c>
       <c r="D79">
-        <v>2735.399863567485</v>
+        <v>2736.435453355336</v>
       </c>
       <c r="E79">
-        <v>1415.438</v>
+        <v>1443.232</v>
       </c>
       <c r="F79">
-        <v>2140.138</v>
+        <v>2167.932</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7765,28 +7765,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M79">
-        <v>162.2224604</v>
+        <v>164.3292456</v>
       </c>
       <c r="N79">
-        <v>195.5575395999999</v>
+        <v>193.4507543999999</v>
       </c>
       <c r="O79">
-        <v>48.88938489999997</v>
+        <v>48.36268859999998</v>
       </c>
       <c r="P79">
-        <v>146.6681546999999</v>
+        <v>145.0880657999999</v>
       </c>
       <c r="Q79">
-        <v>150.3881546999999</v>
+        <v>148.8080657999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2440983384518083</v>
+        <v>0.2524700667849834</v>
       </c>
       <c r="T79">
-        <v>3.86520370892901</v>
+        <v>4.028384276432345</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.205489912542344</v>
+        <v>2.177214400843083</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09988641469269635</v>
+        <v>0.09985571154147681</v>
       </c>
       <c r="C80">
-        <v>568.5034533553362</v>
+        <v>541.745827564062</v>
       </c>
       <c r="D80">
-        <v>2736.435453355336</v>
+        <v>2737.471827564062</v>
       </c>
       <c r="E80">
-        <v>1443.232</v>
+        <v>1471.026</v>
       </c>
       <c r="F80">
-        <v>2167.932</v>
+        <v>2195.726</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7847,28 +7847,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M80">
-        <v>164.3292456</v>
+        <v>166.4360308</v>
       </c>
       <c r="N80">
-        <v>193.4507543999999</v>
+        <v>191.3439691999999</v>
       </c>
       <c r="O80">
-        <v>48.36268859999998</v>
+        <v>47.83599229999998</v>
       </c>
       <c r="P80">
-        <v>145.0880657999999</v>
+        <v>143.5079768999999</v>
       </c>
       <c r="Q80">
-        <v>148.8080657999999</v>
+        <v>147.2279768999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2524700667849834</v>
+        <v>0.261639102578461</v>
       </c>
       <c r="T80">
-        <v>4.028384276432345</v>
+        <v>4.207105850364571</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.177214400843083</v>
+        <v>2.149654724883044</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09985571154147681</v>
+        <v>0.09982500839025725</v>
       </c>
       <c r="C81">
-        <v>541.745827564062</v>
+        <v>514.9889870852558</v>
       </c>
       <c r="D81">
-        <v>2737.471827564062</v>
+        <v>2738.508987085256</v>
       </c>
       <c r="E81">
-        <v>1471.026</v>
+        <v>1498.82</v>
       </c>
       <c r="F81">
-        <v>2195.726</v>
+        <v>2223.52</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7929,28 +7929,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M81">
-        <v>166.4360308</v>
+        <v>168.542816</v>
       </c>
       <c r="N81">
-        <v>191.3439691999999</v>
+        <v>189.2371839999999</v>
       </c>
       <c r="O81">
-        <v>47.83599229999998</v>
+        <v>47.30929599999997</v>
       </c>
       <c r="P81">
-        <v>143.5079768999999</v>
+        <v>141.9278879999999</v>
       </c>
       <c r="Q81">
-        <v>147.2279768999999</v>
+        <v>145.6478879999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.261639102578461</v>
+        <v>0.2717250419512863</v>
       </c>
       <c r="T81">
-        <v>4.207105850364571</v>
+        <v>4.403699581690018</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.149654724883044</v>
+        <v>2.122784040822006</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09982500839025725</v>
+        <v>0.09979430523903769</v>
       </c>
       <c r="C82">
-        <v>514.9889870852558</v>
+        <v>488.2329328118617</v>
       </c>
       <c r="D82">
-        <v>2738.508987085256</v>
+        <v>2739.546932811862</v>
       </c>
       <c r="E82">
-        <v>1498.82</v>
+        <v>1526.614</v>
       </c>
       <c r="F82">
-        <v>2223.52</v>
+        <v>2251.314</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8011,28 +8011,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M82">
-        <v>168.542816</v>
+        <v>170.6496012</v>
       </c>
       <c r="N82">
-        <v>189.2371839999999</v>
+        <v>187.1303987999999</v>
       </c>
       <c r="O82">
-        <v>47.30929599999997</v>
+        <v>46.78259969999998</v>
       </c>
       <c r="P82">
-        <v>141.9278879999999</v>
+        <v>140.3477990999999</v>
       </c>
       <c r="Q82">
-        <v>145.6478879999999</v>
+        <v>144.0677990999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2717250419512863</v>
+        <v>0.28287265915283</v>
       </c>
       <c r="T82">
-        <v>4.403699581690018</v>
+        <v>4.620987389997092</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.122784040822006</v>
+        <v>2.096576830441488</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09979430523903769</v>
+        <v>0.09976360208781815</v>
       </c>
       <c r="C83">
-        <v>488.2329328118617</v>
+        <v>461.4776656381773</v>
       </c>
       <c r="D83">
-        <v>2739.546932811862</v>
+        <v>2740.585665638177</v>
       </c>
       <c r="E83">
-        <v>1526.614</v>
+        <v>1554.408</v>
       </c>
       <c r="F83">
-        <v>2251.314</v>
+        <v>2279.108</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8093,28 +8093,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M83">
-        <v>170.6496012</v>
+        <v>172.7563864</v>
       </c>
       <c r="N83">
-        <v>187.1303987999999</v>
+        <v>185.0236135999999</v>
       </c>
       <c r="O83">
-        <v>46.78259969999998</v>
+        <v>46.25590339999998</v>
       </c>
       <c r="P83">
-        <v>140.3477990999999</v>
+        <v>138.7677102</v>
       </c>
       <c r="Q83">
-        <v>144.0677990999999</v>
+        <v>142.4877102</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.28287265915283</v>
+        <v>0.2952589004878786</v>
       </c>
       <c r="T83">
-        <v>4.620987389997092</v>
+        <v>4.862418288116062</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.096576830441488</v>
+        <v>2.071008820314153</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09976360208781815</v>
+        <v>0.09973289893659859</v>
       </c>
       <c r="C84">
-        <v>461.4776656381773</v>
+        <v>434.723186459858</v>
       </c>
       <c r="D84">
-        <v>2740.585665638177</v>
+        <v>2741.625186459858</v>
       </c>
       <c r="E84">
-        <v>1554.408</v>
+        <v>1582.202</v>
       </c>
       <c r="F84">
-        <v>2279.108</v>
+        <v>2306.902</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8175,28 +8175,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M84">
-        <v>172.7563864</v>
+        <v>174.8631716</v>
       </c>
       <c r="N84">
-        <v>185.0236135999999</v>
+        <v>182.9168283999999</v>
       </c>
       <c r="O84">
-        <v>46.25590339999998</v>
+        <v>45.72920709999998</v>
       </c>
       <c r="P84">
-        <v>138.7677102</v>
+        <v>137.1876212999999</v>
       </c>
       <c r="Q84">
-        <v>142.4877102</v>
+        <v>140.9076212999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2952589004878786</v>
+        <v>0.3091023466858742</v>
       </c>
       <c r="T84">
-        <v>4.862418288116062</v>
+        <v>5.132252821307854</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.071008820314153</v>
+        <v>2.046056906816392</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09973289893659859</v>
+        <v>0.09970219578537905</v>
       </c>
       <c r="C85">
-        <v>434.723186459858</v>
+        <v>407.9694961739178</v>
       </c>
       <c r="D85">
-        <v>2741.625186459858</v>
+        <v>2742.665496173918</v>
       </c>
       <c r="E85">
-        <v>1582.202</v>
+        <v>1609.996</v>
       </c>
       <c r="F85">
-        <v>2306.902</v>
+        <v>2334.696</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8257,28 +8257,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M85">
-        <v>174.8631716</v>
+        <v>176.9699568</v>
       </c>
       <c r="N85">
-        <v>182.9168283999999</v>
+        <v>180.8100431999999</v>
       </c>
       <c r="O85">
-        <v>45.72920709999998</v>
+        <v>45.20251079999998</v>
       </c>
       <c r="P85">
-        <v>137.1876212999999</v>
+        <v>135.6075323999999</v>
       </c>
       <c r="Q85">
-        <v>140.9076212999999</v>
+        <v>139.3275323999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3091023466858742</v>
+        <v>0.3246762236586191</v>
       </c>
       <c r="T85">
-        <v>5.132252821307854</v>
+        <v>5.435816671148618</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.046056906816392</v>
+        <v>2.021699086497149</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09970219578537903</v>
+        <v>0.1087239926341595</v>
       </c>
       <c r="C86">
-        <v>407.9694961739192</v>
+        <v>105.0511243597457</v>
       </c>
       <c r="D86">
-        <v>2742.665496173919</v>
+        <v>2467.541124359745</v>
       </c>
       <c r="E86">
-        <v>1609.995999999999</v>
+        <v>1637.79</v>
       </c>
       <c r="F86">
-        <v>2334.695999999999</v>
+        <v>2362.49</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8339,45 +8339,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M86">
-        <v>176.9699568</v>
+        <v>212.6241</v>
       </c>
       <c r="N86">
-        <v>180.8100431999999</v>
+        <v>145.1558999999999</v>
       </c>
       <c r="O86">
-        <v>45.20251079999998</v>
+        <v>36.28897499999999</v>
       </c>
       <c r="P86">
-        <v>135.6075324</v>
+        <v>108.866925</v>
       </c>
       <c r="Q86">
-        <v>139.3275324</v>
+        <v>112.586925</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3246762236586189</v>
+        <v>0.3423266175610632</v>
       </c>
       <c r="T86">
-        <v>5.435816671148614</v>
+        <v>5.779855700968148</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.021699086497149</v>
+        <v>1.682687898502568</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1087239926341595</v>
+        <v>0.1087997894829399</v>
       </c>
       <c r="C87">
-        <v>105.0511243597457</v>
+        <v>75.17928070375774</v>
       </c>
       <c r="D87">
-        <v>2467.541124359745</v>
+        <v>2465.463280703757</v>
       </c>
       <c r="E87">
-        <v>1637.79</v>
+        <v>1665.584</v>
       </c>
       <c r="F87">
-        <v>2362.49</v>
+        <v>2390.284</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8421,28 +8421,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M87">
-        <v>212.6241</v>
+        <v>215.12556</v>
       </c>
       <c r="N87">
-        <v>145.1558999999999</v>
+        <v>142.65444</v>
       </c>
       <c r="O87">
-        <v>36.28897499999999</v>
+        <v>35.66360999999999</v>
       </c>
       <c r="P87">
-        <v>108.866925</v>
+        <v>106.99083</v>
       </c>
       <c r="Q87">
-        <v>112.586925</v>
+        <v>110.71083</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3423266175610632</v>
+        <v>0.3624984963067137</v>
       </c>
       <c r="T87">
-        <v>5.779855700968148</v>
+        <v>6.173043163619042</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.682687898502568</v>
+        <v>1.663121760147888</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1087997894829399</v>
+        <v>0.1088755863317204</v>
       </c>
       <c r="C88">
-        <v>75.17928070375774</v>
+        <v>45.31093348532977</v>
       </c>
       <c r="D88">
-        <v>2465.463280703757</v>
+        <v>2463.388933485329</v>
       </c>
       <c r="E88">
-        <v>1665.584</v>
+        <v>1693.377999999999</v>
       </c>
       <c r="F88">
-        <v>2390.284</v>
+        <v>2418.078</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8503,28 +8503,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M88">
-        <v>215.12556</v>
+        <v>217.62702</v>
       </c>
       <c r="N88">
-        <v>142.65444</v>
+        <v>140.15298</v>
       </c>
       <c r="O88">
-        <v>35.66360999999999</v>
+        <v>35.03824499999999</v>
       </c>
       <c r="P88">
-        <v>106.99083</v>
+        <v>105.114735</v>
       </c>
       <c r="Q88">
-        <v>110.71083</v>
+        <v>108.834735</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3624984963067137</v>
+        <v>0.3857737410132336</v>
       </c>
       <c r="T88">
-        <v>6.173043163619042</v>
+        <v>6.626721005139304</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.663121760147888</v>
+        <v>1.644005418077222</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1088755863317204</v>
+        <v>0.1089513831805008</v>
       </c>
       <c r="C89">
-        <v>45.31093348532977</v>
+        <v>15.44607388656914</v>
       </c>
       <c r="D89">
-        <v>2463.388933485329</v>
+        <v>2461.318073886569</v>
       </c>
       <c r="E89">
-        <v>1693.377999999999</v>
+        <v>1721.172</v>
       </c>
       <c r="F89">
-        <v>2418.078</v>
+        <v>2445.872</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8585,28 +8585,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M89">
-        <v>217.62702</v>
+        <v>220.12848</v>
       </c>
       <c r="N89">
-        <v>140.15298</v>
+        <v>137.6515199999999</v>
       </c>
       <c r="O89">
-        <v>35.03824499999999</v>
+        <v>34.41287999999999</v>
       </c>
       <c r="P89">
-        <v>105.114735</v>
+        <v>103.23864</v>
       </c>
       <c r="Q89">
-        <v>108.834735</v>
+        <v>106.95864</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3857737410132336</v>
+        <v>0.4129281931708401</v>
       </c>
       <c r="T89">
-        <v>6.626721005139304</v>
+        <v>7.156011820246278</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.644005418077222</v>
+        <v>1.625323538326345</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1089513831805008</v>
+        <v>0.1090271800292813</v>
       </c>
       <c r="C90">
-        <v>15.44607388656914</v>
+        <v>-14.41530688078547</v>
       </c>
       <c r="D90">
-        <v>2461.318073886569</v>
+        <v>2459.250693119214</v>
       </c>
       <c r="E90">
-        <v>1721.172</v>
+        <v>1748.966</v>
       </c>
       <c r="F90">
-        <v>2445.872</v>
+        <v>2473.666</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8667,28 +8667,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M90">
-        <v>220.12848</v>
+        <v>222.62994</v>
       </c>
       <c r="N90">
-        <v>137.6515199999999</v>
+        <v>135.1500599999999</v>
       </c>
       <c r="O90">
-        <v>34.41287999999999</v>
+        <v>33.78751499999998</v>
       </c>
       <c r="P90">
-        <v>103.23864</v>
+        <v>101.362545</v>
       </c>
       <c r="Q90">
-        <v>106.95864</v>
+        <v>105.082545</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4129281931708401</v>
+        <v>0.4450198184480115</v>
       </c>
       <c r="T90">
-        <v>7.156011820246278</v>
+        <v>7.781537329009065</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.625323538326345</v>
+        <v>1.607061476097959</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1090271800292813</v>
+        <v>0.1091029768780617</v>
       </c>
       <c r="C91">
-        <v>-14.41530688078547</v>
+        <v>-44.27321757549771</v>
       </c>
       <c r="D91">
-        <v>2459.250693119214</v>
+        <v>2457.186782424502</v>
       </c>
       <c r="E91">
-        <v>1748.966</v>
+        <v>1776.76</v>
       </c>
       <c r="F91">
-        <v>2473.666</v>
+        <v>2501.46</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8749,28 +8749,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M91">
-        <v>222.62994</v>
+        <v>225.1314</v>
       </c>
       <c r="N91">
-        <v>135.1500599999999</v>
+        <v>132.6486</v>
       </c>
       <c r="O91">
-        <v>33.78751499999998</v>
+        <v>33.16214999999999</v>
       </c>
       <c r="P91">
-        <v>101.362545</v>
+        <v>99.48644999999996</v>
       </c>
       <c r="Q91">
-        <v>105.082545</v>
+        <v>103.20645</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4450198184480115</v>
+        <v>0.4835297687806172</v>
       </c>
       <c r="T91">
-        <v>7.781537329009065</v>
+        <v>8.532167939524411</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.607061476097959</v>
+        <v>1.589205237474648</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1091029768780617</v>
+        <v>0.1091787737268421</v>
       </c>
       <c r="C92">
-        <v>-44.27321757549771</v>
+        <v>-74.12766692695095</v>
       </c>
       <c r="D92">
-        <v>2457.186782424502</v>
+        <v>2455.126333073049</v>
       </c>
       <c r="E92">
-        <v>1776.76</v>
+        <v>1804.554</v>
       </c>
       <c r="F92">
-        <v>2501.46</v>
+        <v>2529.254</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8831,28 +8831,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M92">
-        <v>225.1314</v>
+        <v>227.63286</v>
       </c>
       <c r="N92">
-        <v>132.6486</v>
+        <v>130.1471399999999</v>
       </c>
       <c r="O92">
-        <v>33.16214999999999</v>
+        <v>32.53678499999998</v>
       </c>
       <c r="P92">
-        <v>99.48644999999996</v>
+        <v>97.61035499999994</v>
       </c>
       <c r="Q92">
-        <v>103.20645</v>
+        <v>101.3303549999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4835297687806172</v>
+        <v>0.5305974858538018</v>
       </c>
       <c r="T92">
-        <v>8.532167939524411</v>
+        <v>9.449605352376498</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.589205237474648</v>
+        <v>1.571741443656245</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1091787737268421</v>
+        <v>0.1092545705756226</v>
       </c>
       <c r="C93">
-        <v>-74.12766692695095</v>
+        <v>-103.9786636352746</v>
       </c>
       <c r="D93">
-        <v>2455.126333073049</v>
+        <v>2453.069336364725</v>
       </c>
       <c r="E93">
-        <v>1804.554</v>
+        <v>1832.348</v>
       </c>
       <c r="F93">
-        <v>2529.254</v>
+        <v>2557.048</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8913,28 +8913,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M93">
-        <v>227.63286</v>
+        <v>230.13432</v>
       </c>
       <c r="N93">
-        <v>130.1471399999999</v>
+        <v>127.6456799999999</v>
       </c>
       <c r="O93">
-        <v>32.53678499999998</v>
+        <v>31.91141999999999</v>
       </c>
       <c r="P93">
-        <v>97.61035499999994</v>
+        <v>95.73425999999995</v>
       </c>
       <c r="Q93">
-        <v>101.3303549999999</v>
+        <v>99.45425999999995</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5305974858538018</v>
+        <v>0.5894321321952827</v>
       </c>
       <c r="T93">
-        <v>9.449605352376498</v>
+        <v>10.59640211844161</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.571741443656245</v>
+        <v>1.554657297529547</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1092545705756226</v>
+        <v>0.1093303674244031</v>
       </c>
       <c r="C94">
-        <v>-103.9786636352746</v>
+        <v>-133.8262163714639</v>
       </c>
       <c r="D94">
-        <v>2453.069336364725</v>
+        <v>2451.015783628536</v>
       </c>
       <c r="E94">
-        <v>1832.348</v>
+        <v>1860.142</v>
       </c>
       <c r="F94">
-        <v>2557.048</v>
+        <v>2584.842</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8995,28 +8995,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M94">
-        <v>230.13432</v>
+        <v>232.63578</v>
       </c>
       <c r="N94">
-        <v>127.6456799999999</v>
+        <v>125.14422</v>
       </c>
       <c r="O94">
-        <v>31.91141999999999</v>
+        <v>31.28605499999999</v>
       </c>
       <c r="P94">
-        <v>95.73425999999995</v>
+        <v>93.85816499999997</v>
       </c>
       <c r="Q94">
-        <v>99.45425999999995</v>
+        <v>97.57816499999997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5894321321952827</v>
+        <v>0.6650766774914725</v>
       </c>
       <c r="T94">
-        <v>10.59640211844161</v>
+        <v>12.07085510338247</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.554657297529547</v>
+        <v>1.537940552394821</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1093303674244031</v>
+        <v>0.1094061642731835</v>
       </c>
       <c r="C95">
-        <v>-133.8262163714639</v>
+        <v>-163.6703337775039</v>
       </c>
       <c r="D95">
-        <v>2451.015783628536</v>
+        <v>2448.965666222496</v>
       </c>
       <c r="E95">
-        <v>1860.142</v>
+        <v>1887.936</v>
       </c>
       <c r="F95">
-        <v>2584.842</v>
+        <v>2612.636</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9077,28 +9077,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M95">
-        <v>232.63578</v>
+        <v>235.13724</v>
       </c>
       <c r="N95">
-        <v>125.14422</v>
+        <v>122.6427599999999</v>
       </c>
       <c r="O95">
-        <v>31.28605499999999</v>
+        <v>30.66068999999998</v>
       </c>
       <c r="P95">
-        <v>93.85816499999997</v>
+        <v>91.98206999999994</v>
       </c>
       <c r="Q95">
-        <v>97.57816499999997</v>
+        <v>95.70206999999994</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6650766774914725</v>
+        <v>0.7659360712197254</v>
       </c>
       <c r="T95">
-        <v>12.07085510338247</v>
+        <v>14.03679241663694</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.537940552394821</v>
+        <v>1.521579482688493</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1094061642731835</v>
+        <v>0.109481961121964</v>
       </c>
       <c r="C96">
-        <v>-163.6703337775039</v>
+        <v>-193.5110244664916</v>
       </c>
       <c r="D96">
-        <v>2448.965666222496</v>
+        <v>2446.918975533508</v>
       </c>
       <c r="E96">
-        <v>1887.936</v>
+        <v>1915.73</v>
       </c>
       <c r="F96">
-        <v>2612.636</v>
+        <v>2640.43</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9159,28 +9159,28 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M96">
-        <v>235.13724</v>
+        <v>237.6387</v>
       </c>
       <c r="N96">
-        <v>122.6427599999999</v>
+        <v>120.1412999999999</v>
       </c>
       <c r="O96">
-        <v>30.66068999999998</v>
+        <v>30.03532499999999</v>
       </c>
       <c r="P96">
-        <v>91.98206999999994</v>
+        <v>90.10597499999996</v>
       </c>
       <c r="Q96">
-        <v>95.70206999999994</v>
+        <v>93.82597499999996</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7659360712197254</v>
+        <v>0.9071392224392799</v>
       </c>
       <c r="T96">
-        <v>14.03679241663694</v>
+        <v>16.78910465519321</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.521579482688493</v>
+        <v>1.505562856554929</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.109481961121964</v>
+        <v>0.1546780671096485</v>
       </c>
       <c r="C97">
-        <v>-193.5110244664916</v>
+        <v>-1035.129443140236</v>
       </c>
       <c r="D97">
-        <v>2446.918975533508</v>
+        <v>1633.094556859763</v>
       </c>
       <c r="E97">
-        <v>1915.73</v>
+        <v>1943.524</v>
       </c>
       <c r="F97">
-        <v>2640.43</v>
+        <v>2668.224</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9241,45 +9241,45 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M97">
-        <v>237.6387</v>
+        <v>391.6952832</v>
       </c>
       <c r="N97">
-        <v>120.1412999999999</v>
+        <v>-33.91528320000009</v>
       </c>
       <c r="O97">
-        <v>30.03532499999999</v>
+        <v>-8.478820800000022</v>
       </c>
       <c r="P97">
-        <v>90.10597499999996</v>
+        <v>-25.43646240000007</v>
       </c>
       <c r="Q97">
-        <v>93.82597499999996</v>
+        <v>-21.71646240000007</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9071392224392799</v>
+        <v>1.148286829212755</v>
       </c>
       <c r="T97">
-        <v>16.78910465519321</v>
+        <v>21.48952035901269</v>
       </c>
       <c r="U97">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.25</v>
+        <v>0.22835352846036</v>
       </c>
       <c r="W97">
-        <v>0.0675</v>
+        <v>0.1132777020220192</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.505562856554929</v>
+        <v>0.9134141138414401</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1546780671096485</v>
+        <v>0.1556880671096485</v>
       </c>
       <c r="C98">
-        <v>-1035.129443140236</v>
+        <v>-1074.971773927965</v>
       </c>
       <c r="D98">
-        <v>1633.094556859763</v>
+        <v>1621.046226072035</v>
       </c>
       <c r="E98">
-        <v>1943.524</v>
+        <v>1971.318</v>
       </c>
       <c r="F98">
-        <v>2668.224</v>
+        <v>2696.018</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9323,37 +9323,37 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M98">
-        <v>391.6952832</v>
+        <v>395.7754424</v>
       </c>
       <c r="N98">
-        <v>-33.91528320000009</v>
+        <v>-37.99544240000006</v>
       </c>
       <c r="O98">
-        <v>-8.478820800000022</v>
+        <v>-9.498860600000015</v>
       </c>
       <c r="P98">
-        <v>-25.43646240000007</v>
+        <v>-28.49658180000004</v>
       </c>
       <c r="Q98">
-        <v>-21.71646240000007</v>
+        <v>-24.77658180000005</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.148286829212752</v>
+        <v>1.515782438950336</v>
       </c>
       <c r="T98">
-        <v>21.48952035901263</v>
+        <v>28.65269381201684</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.22835352846036</v>
+        <v>0.2259993683731398</v>
       </c>
       <c r="W98">
-        <v>0.1132777020220192</v>
+        <v>0.1136232927228231</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9134141138414401</v>
+        <v>0.9039974734925593</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1556880671096485</v>
+        <v>0.1566980671096485</v>
       </c>
       <c r="C99">
-        <v>-1074.971773927965</v>
+        <v>-1114.637630956652</v>
       </c>
       <c r="D99">
-        <v>1621.046226072035</v>
+        <v>1609.174369043347</v>
       </c>
       <c r="E99">
-        <v>1971.318</v>
+        <v>1999.111999999999</v>
       </c>
       <c r="F99">
-        <v>2696.018</v>
+        <v>2723.811999999999</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9405,37 +9405,37 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M99">
-        <v>395.7754424</v>
+        <v>399.8556015999999</v>
       </c>
       <c r="N99">
-        <v>-37.99544240000006</v>
+        <v>-42.07560160000003</v>
       </c>
       <c r="O99">
-        <v>-9.498860600000015</v>
+        <v>-10.51890040000001</v>
       </c>
       <c r="P99">
-        <v>-28.49658180000004</v>
+        <v>-31.55670120000002</v>
       </c>
       <c r="Q99">
-        <v>-24.77658180000005</v>
+        <v>-27.83670120000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.515782438950336</v>
+        <v>2.250773658425503</v>
       </c>
       <c r="T99">
-        <v>28.65269381201684</v>
+        <v>42.97904071802526</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2259993683731398</v>
+        <v>0.2236932523693323</v>
       </c>
       <c r="W99">
-        <v>0.1136232927228231</v>
+        <v>0.113961830552182</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9039974734925593</v>
+        <v>0.8947730094773292</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1566980671096485</v>
+        <v>0.1577080671096485</v>
       </c>
       <c r="C100">
-        <v>-1114.637630956652</v>
+        <v>-1154.130863294895</v>
       </c>
       <c r="D100">
-        <v>1609.174369043347</v>
+        <v>1597.475136705105</v>
       </c>
       <c r="E100">
-        <v>1999.111999999999</v>
+        <v>2026.906</v>
       </c>
       <c r="F100">
-        <v>2723.811999999999</v>
+        <v>2751.606</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9487,37 +9487,37 @@
         <v>357.7799999999999</v>
       </c>
       <c r="M100">
-        <v>399.8556015999999</v>
+        <v>403.9357608</v>
       </c>
       <c r="N100">
-        <v>-42.07560160000003</v>
+        <v>-46.15576080000011</v>
       </c>
       <c r="O100">
-        <v>-10.51890040000001</v>
+        <v>-11.53894020000003</v>
       </c>
       <c r="P100">
-        <v>-31.55670120000002</v>
+        <v>-34.61682060000008</v>
       </c>
       <c r="Q100">
-        <v>-27.83670120000002</v>
+        <v>-30.89682060000008</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.250773658425503</v>
+        <v>4.455747316851006</v>
       </c>
       <c r="T100">
-        <v>42.97904071802526</v>
+        <v>85.95808143605052</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2236932523693323</v>
+        <v>0.2214337245676218</v>
       </c>
       <c r="W100">
-        <v>0.113961830552182</v>
+        <v>0.1142935292334731</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8947730094773292</v>
+        <v>0.8857348982704873</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1577080671096485</v>
-      </c>
-      <c r="C101">
-        <v>-1154.130863294895</v>
-      </c>
-      <c r="D101">
-        <v>1597.475136705105</v>
-      </c>
-      <c r="E101">
-        <v>2026.906</v>
-      </c>
-      <c r="F101">
-        <v>2751.606</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>2054.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>361.4999999999999</v>
-      </c>
-      <c r="K101">
-        <v>3.72</v>
-      </c>
-      <c r="L101">
-        <v>357.7799999999999</v>
-      </c>
-      <c r="M101">
-        <v>403.9357608</v>
-      </c>
-      <c r="N101">
-        <v>-46.15576080000011</v>
-      </c>
-      <c r="O101">
-        <v>-11.53894020000003</v>
-      </c>
-      <c r="P101">
-        <v>-34.61682060000008</v>
-      </c>
-      <c r="Q101">
-        <v>-30.89682060000008</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.455747316851006</v>
-      </c>
-      <c r="T101">
-        <v>85.95808143605052</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2214337245676218</v>
-      </c>
-      <c r="W101">
-        <v>0.1142935292334731</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8857348982704873</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
